--- a/EF-45_REST_API_specification_v1.4.10_210201.xlsx
+++ b/EF-45_REST_API_specification_v1.4.10_210201.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_C-data\1_기술문서\01_모델별\EF-45\1_신규\2_추가문서\REST\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAEA981-C3D5-4277-BDFC-42EFD2467851}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="914" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="11760" tabRatio="914" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Revision_History" sheetId="17" r:id="rId1"/>
@@ -36,27 +30,18 @@
     <sheet name="User-schedule" sheetId="21" r:id="rId21"/>
     <sheet name="Schedule" sheetId="22" r:id="rId22"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="125725"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>scott lee</author>
   </authors>
   <commentList>
-    <comment ref="I88" authorId="0" shapeId="0" xr:uid="{4B733CFB-75D3-498C-AC7F-957A138F104E}">
+    <comment ref="I88" authorId="0">
       <text>
         <r>
           <rPr>
@@ -80,7 +65,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I89" authorId="0" shapeId="0" xr:uid="{B7ED972F-BD4A-42ED-91BC-E373CA4F111F}">
+    <comment ref="I89" authorId="0">
       <text>
         <r>
           <rPr>
@@ -113,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I90" authorId="0" shapeId="0" xr:uid="{1A9EB48B-EADB-4F45-96C0-E543E049D29A}">
+    <comment ref="I90" authorId="0">
       <text>
         <r>
           <rPr>
@@ -142,12 +127,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>bkko</author>
   </authors>
   <commentList>
-    <comment ref="M15" authorId="0" shapeId="0" xr:uid="{CFF0D823-BD13-4823-9697-43195B719FDC}">
+    <comment ref="M15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -297,7 +282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M48" authorId="0" shapeId="0" xr:uid="{018BB183-0594-4B61-8614-F11E8CB15E90}">
+    <comment ref="M48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2427,51 +2412,6 @@
   </si>
   <si>
     <r>
-      <t>http://{host}/1.0/biometric-data/save-8bmp?lock_uid={lock_uid}  :</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> for Black &amp; White 8bit Iris image</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-http://{host}/1.0/biometric-data/save-24bmp?lock_uid={lock_uid}  : </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>for Color 24bit Face image</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;Iris&gt;
-• URL Example: http://192.168.0.100:9980/1.0/biometric-data/save-8bmp?lock_uid=13dbb896-ed1e-11e6-9822-503f98000109
-• Body Example: {"filename":"/usr/local/share/CMITECH/Images/righteye.bmp","height":"480","image":"","width":"640"}
-&lt;Face&gt;
-• URL Example: http://192.168.0.100:9980/1.0/biometric-data/save-24bmp?lock_uid=13dbb896-ed1e-11e6-9822-503f98000109
-• Body Example: {"filename":"/usr/local/share/CMITECH/Images/faroff.bmp","height":"916","image":"","width":"688"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>•</t>
     </r>
     <r>
@@ -5650,13 +5590,56 @@
     <t>rightPupilDiameter</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>&lt;Iris&gt;
+• URL Example: http://192.168.0.100:9980/1.0/biometric-data/save-8bmp?lock_uid=13dbb896-ed1e-11e6-9822-503f98000109
+• Body Example: {"filename":"/usr/local/share/CMITECH/Images/righteye.bmp","height":"480","image":"","width":"640"}
+&lt;Face&gt;
+• URL Example: http://192.168.0.100:9980/1.0/biometric-data/save-24bmp?lock_uid=13dbb896-ed1e-11e6-9822-503f98000109
+• Body Example: {"filename":"/usr/local/share/CMITECH/Images/faroff.bmp","height":"916","image":"","width":"688"}</t>
+  </si>
+  <si>
+    <r>
+      <t>http://{host}/1.0/biometric-data/save-8bmp?lock_uid={lock_uid}  :</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> for Black &amp; White 8bit Iris image</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+http://{host}/1.0/biometric-data/save-24bmp?lock_uid={lock_uid}  : </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>for Color 24bit Face image</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="[$₩-412]#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="[$₩-412]#,##0.00"/>
   </numFmts>
   <fonts count="47">
     <font>
@@ -6857,7 +6840,7 @@
     <xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8215,9 +8198,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="1" xr:uid="{D7668087-D142-4558-874B-38F3F3762F90}"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8226,14 +8209,6 @@
       <color rgb="FF0000FF"/>
     </mruColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -8280,7 +8255,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -8332,7 +8307,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -8526,14 +8501,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0439F1F7-41BC-4444-9A57-239575B43785}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I41"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -8566,7 +8541,7 @@
     </row>
     <row r="2" spans="1:9" ht="16.5" customHeight="1">
       <c r="B2" s="329" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C2" s="330"/>
       <c r="D2" s="330"/>
@@ -8578,7 +8553,7 @@
     </row>
     <row r="3" spans="1:9" ht="16.5" customHeight="1">
       <c r="B3" s="181" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>276</v>
@@ -8594,10 +8569,10 @@
     </row>
     <row r="4" spans="1:9" ht="16.5" customHeight="1">
       <c r="B4" s="182" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C4" s="191" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D4" s="102"/>
       <c r="E4" s="88"/>
@@ -8608,10 +8583,10 @@
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1">
       <c r="B5" s="183" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C5" s="191" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D5" s="102"/>
       <c r="E5" s="88"/>
@@ -8621,13 +8596,13 @@
     </row>
     <row r="6" spans="1:9" ht="40.5" customHeight="1">
       <c r="B6" s="183" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C6" s="186" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D6" s="186" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E6" s="88"/>
       <c r="F6" s="88"/>
@@ -8636,13 +8611,13 @@
     </row>
     <row r="7" spans="1:9" ht="49.5" customHeight="1">
       <c r="B7" s="331" t="s">
+        <v>734</v>
+      </c>
+      <c r="C7" s="191" t="s">
+        <v>735</v>
+      </c>
+      <c r="D7" s="187" t="s">
         <v>736</v>
-      </c>
-      <c r="C7" s="191" t="s">
-        <v>737</v>
-      </c>
-      <c r="D7" s="187" t="s">
-        <v>738</v>
       </c>
       <c r="E7" s="88"/>
       <c r="F7" s="88"/>
@@ -8652,10 +8627,10 @@
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
       <c r="B8" s="332"/>
       <c r="C8" s="191" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D8" s="102" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E8" s="88"/>
       <c r="F8" s="88"/>
@@ -8665,7 +8640,7 @@
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="B9" s="332"/>
       <c r="C9" s="191" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D9" s="102"/>
       <c r="E9" s="88"/>
@@ -8684,10 +8659,10 @@
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
       <c r="B11" s="183" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C11" s="191" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D11" s="102"/>
       <c r="E11" s="88"/>
@@ -8697,10 +8672,10 @@
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
       <c r="B12" s="184" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C12" s="191" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D12" s="102"/>
       <c r="E12" s="88"/>
@@ -8710,10 +8685,10 @@
     </row>
     <row r="13" spans="1:9" ht="31.5" customHeight="1">
       <c r="B13" s="183" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C13" s="186" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D13" s="102"/>
       <c r="E13" s="88"/>
@@ -8723,13 +8698,13 @@
     </row>
     <row r="14" spans="1:9" ht="42.75" customHeight="1">
       <c r="B14" s="183" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C14" s="186" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="D14" s="186" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E14" s="88"/>
       <c r="F14" s="88"/>
@@ -8738,10 +8713,10 @@
     </row>
     <row r="15" spans="1:9" ht="30.75" customHeight="1">
       <c r="B15" s="183" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C15" s="186" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D15" s="102"/>
       <c r="E15" s="88"/>
@@ -8751,10 +8726,10 @@
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1">
       <c r="B16" s="183" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C16" s="191" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D16" s="102"/>
       <c r="E16" s="88"/>
@@ -8764,10 +8739,10 @@
     </row>
     <row r="17" spans="2:9" ht="19.5" customHeight="1">
       <c r="B17" s="331" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C17" s="191" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D17" s="102"/>
       <c r="E17" s="88"/>
@@ -8778,7 +8753,7 @@
     <row r="18" spans="2:9" ht="32.25" customHeight="1">
       <c r="B18" s="333"/>
       <c r="C18" s="186" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D18" s="102"/>
       <c r="E18" s="88"/>
@@ -8788,10 +8763,10 @@
     </row>
     <row r="19" spans="2:9" ht="15.75" customHeight="1">
       <c r="B19" s="184" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C19" s="191" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="D19" s="102"/>
       <c r="E19" s="88"/>
@@ -8801,13 +8776,13 @@
     </row>
     <row r="20" spans="2:9" ht="30.75" customHeight="1">
       <c r="B20" s="183" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C20" s="191" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D20" s="187" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="E20" s="88"/>
       <c r="F20" s="88"/>
@@ -8816,13 +8791,13 @@
     </row>
     <row r="21" spans="2:9" s="253" customFormat="1" ht="31.5" customHeight="1">
       <c r="B21" s="183" t="s">
+        <v>907</v>
+      </c>
+      <c r="C21" s="191" t="s">
         <v>909</v>
       </c>
-      <c r="C21" s="191" t="s">
-        <v>911</v>
-      </c>
       <c r="D21" s="187" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E21" s="88"/>
       <c r="F21" s="88"/>
@@ -8831,13 +8806,13 @@
     </row>
     <row r="22" spans="2:9" s="253" customFormat="1" ht="31.5" customHeight="1">
       <c r="B22" s="183" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C22" s="191" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="D22" s="187" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E22" s="88"/>
       <c r="F22" s="88"/>
@@ -8846,10 +8821,10 @@
     </row>
     <row r="23" spans="2:9" s="253" customFormat="1" ht="15.75" customHeight="1">
       <c r="B23" s="183" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C23" s="191" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D23" s="102"/>
       <c r="E23" s="88"/>
@@ -8859,13 +8834,13 @@
     </row>
     <row r="24" spans="2:9" s="253" customFormat="1" ht="35.25" customHeight="1">
       <c r="B24" s="183" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C24" s="191" t="s">
+        <v>921</v>
+      </c>
+      <c r="D24" s="187" t="s">
         <v>923</v>
-      </c>
-      <c r="D24" s="187" t="s">
-        <v>925</v>
       </c>
       <c r="E24" s="88"/>
       <c r="F24" s="88"/>
@@ -8874,13 +8849,13 @@
     </row>
     <row r="25" spans="2:9" s="253" customFormat="1" ht="33" customHeight="1">
       <c r="B25" s="183" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C25" s="191" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="D25" s="187" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="E25" s="88"/>
       <c r="F25" s="88"/>
@@ -8889,13 +8864,13 @@
     </row>
     <row r="26" spans="2:9" s="253" customFormat="1" ht="30.75" customHeight="1">
       <c r="B26" s="183" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C26" s="191" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D26" s="187" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="E26" s="88"/>
       <c r="F26" s="88"/>
@@ -8904,13 +8879,13 @@
     </row>
     <row r="27" spans="2:9" s="271" customFormat="1" ht="30.75" customHeight="1">
       <c r="B27" s="183" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C27" s="191" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="D27" s="187" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="E27" s="88"/>
       <c r="F27" s="88"/>
@@ -8919,10 +8894,10 @@
     </row>
     <row r="28" spans="2:9" s="271" customFormat="1" ht="32.25" customHeight="1">
       <c r="B28" s="183" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C28" s="186" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="D28" s="102"/>
       <c r="E28" s="88"/>
@@ -8932,13 +8907,13 @@
     </row>
     <row r="29" spans="2:9" s="271" customFormat="1" ht="30" customHeight="1">
       <c r="B29" s="183" t="s">
+        <v>992</v>
+      </c>
+      <c r="C29" s="191" t="s">
+        <v>993</v>
+      </c>
+      <c r="D29" s="187" t="s">
         <v>994</v>
-      </c>
-      <c r="C29" s="191" t="s">
-        <v>995</v>
-      </c>
-      <c r="D29" s="187" t="s">
-        <v>996</v>
       </c>
       <c r="E29" s="88"/>
       <c r="F29" s="88"/>
@@ -8947,13 +8922,13 @@
     </row>
     <row r="30" spans="2:9" s="271" customFormat="1" ht="32.25" customHeight="1">
       <c r="B30" s="183" t="s">
+        <v>996</v>
+      </c>
+      <c r="C30" s="191" t="s">
+        <v>997</v>
+      </c>
+      <c r="D30" s="187" t="s">
         <v>998</v>
-      </c>
-      <c r="C30" s="191" t="s">
-        <v>999</v>
-      </c>
-      <c r="D30" s="187" t="s">
-        <v>1000</v>
       </c>
       <c r="E30" s="88"/>
       <c r="F30" s="88"/>
@@ -8962,13 +8937,13 @@
     </row>
     <row r="31" spans="2:9" s="306" customFormat="1" ht="32.25" customHeight="1">
       <c r="B31" s="183" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C31" s="191" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D31" s="187" t="s">
         <v>1002</v>
-      </c>
-      <c r="C31" s="191" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D31" s="187" t="s">
-        <v>1004</v>
       </c>
       <c r="E31" s="88"/>
       <c r="F31" s="88"/>
@@ -8977,10 +8952,10 @@
     </row>
     <row r="32" spans="2:9" s="309" customFormat="1" ht="32.25" customHeight="1">
       <c r="B32" s="183" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C32" s="186" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="D32" s="187"/>
       <c r="E32" s="88"/>
@@ -8990,13 +8965,13 @@
     </row>
     <row r="33" spans="2:9" s="310" customFormat="1" ht="32.25" customHeight="1">
       <c r="B33" s="312" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C33" s="186" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="D33" s="187" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E33" s="88"/>
       <c r="F33" s="88"/>
@@ -9005,13 +8980,13 @@
     </row>
     <row r="34" spans="2:9" s="311" customFormat="1" ht="32.25" customHeight="1">
       <c r="B34" s="331" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C34" s="186" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D34" s="187" t="s">
         <v>1020</v>
-      </c>
-      <c r="D34" s="187" t="s">
-        <v>1022</v>
       </c>
       <c r="E34" s="88"/>
       <c r="F34" s="88"/>
@@ -9021,7 +8996,7 @@
     <row r="35" spans="2:9" s="310" customFormat="1" ht="32.25" customHeight="1">
       <c r="B35" s="333"/>
       <c r="C35" s="186" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="D35" s="187"/>
       <c r="E35" s="88"/>
@@ -9031,13 +9006,13 @@
     </row>
     <row r="36" spans="2:9" s="313" customFormat="1" ht="32.25" customHeight="1">
       <c r="B36" s="314" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C36" s="186" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="D36" s="187" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E36" s="88"/>
       <c r="F36" s="88"/>
@@ -9046,13 +9021,13 @@
     </row>
     <row r="37" spans="2:9" s="317" customFormat="1" ht="34.5" customHeight="1">
       <c r="B37" s="318" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C37" s="186" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D37" s="187" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="E37" s="88"/>
       <c r="F37" s="88"/>
@@ -9061,13 +9036,13 @@
     </row>
     <row r="38" spans="2:9" s="317" customFormat="1" ht="43.5" customHeight="1">
       <c r="B38" s="325" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C38" s="186" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D38" s="187" t="s">
         <v>1042</v>
-      </c>
-      <c r="C38" s="186" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D38" s="187" t="s">
-        <v>1044</v>
       </c>
       <c r="E38" s="88"/>
       <c r="F38" s="88"/>
@@ -9076,13 +9051,13 @@
     </row>
     <row r="39" spans="2:9" s="313" customFormat="1" ht="31.5" customHeight="1">
       <c r="B39" s="328" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C39" s="186" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D39" s="187" t="s">
         <v>1048</v>
-      </c>
-      <c r="C39" s="186" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D39" s="187" t="s">
-        <v>1050</v>
       </c>
       <c r="E39" s="88"/>
       <c r="F39" s="88"/>
@@ -9121,7 +9096,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE2AA2D0-1970-4F6F-A1C8-23BA273267C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:M79"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -9141,7 +9116,7 @@
         <v>294</v>
       </c>
       <c r="B2" s="380" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C2" s="355"/>
       <c r="D2" s="341"/>
@@ -9149,7 +9124,7 @@
         <v>293</v>
       </c>
       <c r="F2" s="381" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G2" s="355"/>
       <c r="H2" s="341"/>
@@ -9169,7 +9144,7 @@
         <v>292</v>
       </c>
       <c r="F3" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G3" s="365"/>
       <c r="H3" s="366"/>
@@ -9199,7 +9174,7 @@
         <v>92</v>
       </c>
       <c r="B5" s="359" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C5" s="365"/>
       <c r="D5" s="365"/>
@@ -9218,7 +9193,7 @@
         <v>285</v>
       </c>
       <c r="B6" s="384" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C6" s="355"/>
       <c r="D6" s="355"/>
@@ -9635,7 +9610,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="385" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C24" s="387"/>
       <c r="D24" s="96"/>
@@ -9660,7 +9635,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="453" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C25" s="387"/>
       <c r="D25" s="96"/>
@@ -9685,7 +9660,7 @@
         <v>16</v>
       </c>
       <c r="B26" s="452" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C26" s="185" t="s">
         <v>222</v>
@@ -9913,7 +9888,7 @@
       </c>
       <c r="B35" s="452"/>
       <c r="C35" s="185" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D35" s="96"/>
       <c r="E35" s="89" t="s">
@@ -10087,7 +10062,7 @@
         <v>32</v>
       </c>
       <c r="B42" s="385" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C42" s="387"/>
       <c r="D42" s="96"/>
@@ -10112,7 +10087,7 @@
         <v>33</v>
       </c>
       <c r="B43" s="385" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C43" s="387"/>
       <c r="D43" s="96"/>
@@ -10137,7 +10112,7 @@
         <v>34</v>
       </c>
       <c r="B44" s="385" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C44" s="387"/>
       <c r="D44" s="96"/>
@@ -10162,7 +10137,7 @@
         <v>35</v>
       </c>
       <c r="B45" s="385" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C45" s="387"/>
       <c r="D45" s="96"/>
@@ -10187,7 +10162,7 @@
         <v>36</v>
       </c>
       <c r="B46" s="385" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C46" s="387"/>
       <c r="D46" s="96"/>
@@ -10237,7 +10212,7 @@
         <v>38</v>
       </c>
       <c r="B48" s="452" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C48" s="185" t="s">
         <v>222</v>
@@ -10265,11 +10240,11 @@
       </c>
       <c r="B49" s="452"/>
       <c r="C49" s="185" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D49" s="96"/>
       <c r="E49" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F49" s="92" t="s">
         <v>99</v>
@@ -10290,11 +10265,11 @@
       </c>
       <c r="B50" s="452"/>
       <c r="C50" s="185" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D50" s="96"/>
       <c r="E50" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F50" s="92" t="s">
         <v>99</v>
@@ -10312,7 +10287,7 @@
     <row r="51" spans="1:13" ht="52.5" customHeight="1">
       <c r="A51" s="19"/>
       <c r="B51" s="400" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C51" s="389"/>
       <c r="D51" s="389"/>
@@ -10331,7 +10306,7 @@
         <v>294</v>
       </c>
       <c r="B54" s="380" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C54" s="355"/>
       <c r="D54" s="341"/>
@@ -10339,7 +10314,7 @@
         <v>293</v>
       </c>
       <c r="F54" s="381" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="G54" s="355"/>
       <c r="H54" s="341"/>
@@ -10358,7 +10333,7 @@
         <v>292</v>
       </c>
       <c r="F55" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G55" s="365"/>
       <c r="H55" s="366"/>
@@ -10369,7 +10344,7 @@
         <v>90</v>
       </c>
       <c r="B56" s="379" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C56" s="355"/>
       <c r="D56" s="355"/>
@@ -10388,7 +10363,7 @@
         <v>92</v>
       </c>
       <c r="B57" s="359" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C57" s="365"/>
       <c r="D57" s="365"/>
@@ -10407,7 +10382,7 @@
         <v>285</v>
       </c>
       <c r="B58" s="384" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C58" s="355"/>
       <c r="D58" s="355"/>
@@ -10547,7 +10522,7 @@
     <row r="65" spans="1:13" ht="30.75" customHeight="1">
       <c r="A65" s="19"/>
       <c r="B65" s="385" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C65" s="386"/>
       <c r="D65" s="386"/>
@@ -10581,7 +10556,7 @@
         <v>294</v>
       </c>
       <c r="B68" s="380" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C68" s="355"/>
       <c r="D68" s="341"/>
@@ -10589,7 +10564,7 @@
         <v>293</v>
       </c>
       <c r="F68" s="381" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G68" s="355"/>
       <c r="H68" s="341"/>
@@ -10608,7 +10583,7 @@
         <v>292</v>
       </c>
       <c r="F69" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G69" s="365"/>
       <c r="H69" s="366"/>
@@ -10638,7 +10613,7 @@
         <v>92</v>
       </c>
       <c r="B71" s="359" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C71" s="365"/>
       <c r="D71" s="365"/>
@@ -10657,7 +10632,7 @@
         <v>285</v>
       </c>
       <c r="B72" s="384" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C72" s="355"/>
       <c r="D72" s="355"/>
@@ -10775,7 +10750,7 @@
         <v>2</v>
       </c>
       <c r="B78" s="270" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C78" s="95"/>
       <c r="D78" s="96"/>
@@ -10798,7 +10773,7 @@
     <row r="79" spans="1:13" s="268" customFormat="1" ht="30.75" customHeight="1">
       <c r="A79" s="19"/>
       <c r="B79" s="400" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C79" s="386"/>
       <c r="D79" s="386"/>
@@ -10896,7 +10871,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10AC2E7-F566-44C3-9415-8086180B2528}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M53"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -10917,7 +10892,7 @@
         <v>294</v>
       </c>
       <c r="B2" s="380" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C2" s="355"/>
       <c r="D2" s="341"/>
@@ -10925,7 +10900,7 @@
         <v>293</v>
       </c>
       <c r="F2" s="381" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="G2" s="355"/>
       <c r="H2" s="341"/>
@@ -10944,7 +10919,7 @@
         <v>292</v>
       </c>
       <c r="F3" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G3" s="365"/>
       <c r="H3" s="366"/>
@@ -10974,7 +10949,7 @@
         <v>92</v>
       </c>
       <c r="B5" s="359" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C5" s="365"/>
       <c r="D5" s="365"/>
@@ -11084,7 +11059,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C11" s="95"/>
       <c r="D11" s="96"/>
@@ -11099,7 +11074,7 @@
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="223" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="J11" s="114"/>
       <c r="K11" s="143" t="s">
@@ -11129,14 +11104,14 @@
         <v>95</v>
       </c>
       <c r="H12" s="454" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="I12" s="145" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="J12" s="114"/>
       <c r="K12" s="143" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="L12" s="92" t="s">
         <v>99</v>
@@ -11155,7 +11130,7 @@
       <c r="G13" s="114"/>
       <c r="H13" s="455"/>
       <c r="I13" s="145" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J13" s="114"/>
       <c r="K13" s="143" t="s">
@@ -11178,7 +11153,7 @@
       <c r="G14" s="117"/>
       <c r="H14" s="456"/>
       <c r="I14" s="145" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="J14" s="114"/>
       <c r="K14" s="143" t="s">
@@ -11242,7 +11217,7 @@
     <row r="18" spans="1:13" s="197" customFormat="1">
       <c r="A18" s="19"/>
       <c r="B18" s="385" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C18" s="386"/>
       <c r="D18" s="386"/>
@@ -11276,7 +11251,7 @@
         <v>294</v>
       </c>
       <c r="B21" s="380" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C21" s="355"/>
       <c r="D21" s="341"/>
@@ -11284,7 +11259,7 @@
         <v>293</v>
       </c>
       <c r="F21" s="381" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G21" s="355"/>
       <c r="H21" s="341"/>
@@ -11304,7 +11279,7 @@
         <v>292</v>
       </c>
       <c r="F22" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G22" s="365"/>
       <c r="H22" s="366"/>
@@ -11334,7 +11309,7 @@
         <v>92</v>
       </c>
       <c r="B24" s="359" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C24" s="365"/>
       <c r="D24" s="365"/>
@@ -11353,7 +11328,7 @@
         <v>285</v>
       </c>
       <c r="B25" s="384" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C25" s="355"/>
       <c r="D25" s="355"/>
@@ -11495,7 +11470,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="452" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C32" s="185" t="s">
         <v>222</v>
@@ -11523,11 +11498,11 @@
       </c>
       <c r="B33" s="452"/>
       <c r="C33" s="185" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D33" s="96"/>
       <c r="E33" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F33" s="92" t="s">
         <v>99</v>
@@ -11548,11 +11523,11 @@
       </c>
       <c r="B34" s="452"/>
       <c r="C34" s="185" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D34" s="96"/>
       <c r="E34" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F34" s="92" t="s">
         <v>99</v>
@@ -11570,7 +11545,7 @@
     <row r="35" spans="1:13" ht="52.5" customHeight="1">
       <c r="A35" s="19"/>
       <c r="B35" s="400" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C35" s="389"/>
       <c r="D35" s="389"/>
@@ -11589,7 +11564,7 @@
         <v>294</v>
       </c>
       <c r="B37" s="380" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C37" s="355"/>
       <c r="D37" s="341"/>
@@ -11597,7 +11572,7 @@
         <v>293</v>
       </c>
       <c r="F37" s="381" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="G37" s="355"/>
       <c r="H37" s="341"/>
@@ -11616,7 +11591,7 @@
         <v>292</v>
       </c>
       <c r="F38" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G38" s="365"/>
       <c r="H38" s="366"/>
@@ -11627,7 +11602,7 @@
         <v>90</v>
       </c>
       <c r="B39" s="379" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C39" s="355"/>
       <c r="D39" s="355"/>
@@ -11646,7 +11621,7 @@
         <v>92</v>
       </c>
       <c r="B40" s="359" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C40" s="365"/>
       <c r="D40" s="365"/>
@@ -11756,7 +11731,7 @@
         <v>1</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C46" s="95"/>
       <c r="D46" s="96"/>
@@ -11887,7 +11862,7 @@
     <row r="53" spans="1:13" s="213" customFormat="1">
       <c r="A53" s="19"/>
       <c r="B53" s="385" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C53" s="386"/>
       <c r="D53" s="386"/>
@@ -11960,7 +11935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:M71"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -11980,7 +11955,7 @@
         <v>293</v>
       </c>
       <c r="F2" s="381" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G2" s="355"/>
       <c r="H2" s="341"/>
@@ -12029,7 +12004,7 @@
         <v>92</v>
       </c>
       <c r="B5" s="359" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C5" s="365"/>
       <c r="D5" s="365"/>
@@ -12139,7 +12114,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="89" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C11" s="90"/>
       <c r="D11" s="90"/>
@@ -12272,7 +12247,7 @@
     <row r="16" spans="1:13" ht="16.5">
       <c r="A16" s="19"/>
       <c r="B16" s="471" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C16" s="386"/>
       <c r="D16" s="386"/>
@@ -12289,7 +12264,7 @@
     <row r="17" spans="1:13" ht="30.75" customHeight="1">
       <c r="A17" s="120"/>
       <c r="B17" s="465" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C17" s="468"/>
       <c r="D17" s="468"/>
@@ -12297,7 +12272,7 @@
       <c r="F17" s="468"/>
       <c r="G17" s="469"/>
       <c r="H17" s="470" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I17" s="466"/>
       <c r="J17" s="466"/>
@@ -12318,7 +12293,7 @@
         <v>293</v>
       </c>
       <c r="F20" s="381" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G20" s="355"/>
       <c r="H20" s="341"/>
@@ -12367,7 +12342,7 @@
         <v>92</v>
       </c>
       <c r="B23" s="359" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C23" s="365"/>
       <c r="D23" s="365"/>
@@ -12386,7 +12361,7 @@
         <v>285</v>
       </c>
       <c r="B24" s="384" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C24" s="355"/>
       <c r="D24" s="355"/>
@@ -12494,11 +12469,11 @@
       </c>
       <c r="H29" s="20"/>
       <c r="I29" s="89" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="J29" s="93"/>
       <c r="K29" s="91" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="L29" s="177" t="s">
         <v>99</v>
@@ -12515,11 +12490,11 @@
       <c r="G30" s="19"/>
       <c r="H30" s="94"/>
       <c r="I30" s="46" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="J30" s="95"/>
       <c r="K30" s="91" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="L30" s="92" t="s">
         <v>99</v>
@@ -12536,11 +12511,11 @@
       <c r="G31" s="91"/>
       <c r="H31" s="98"/>
       <c r="I31" s="21" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="J31" s="93"/>
       <c r="K31" s="91" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="L31" s="92" t="s">
         <v>99</v>
@@ -12557,7 +12532,7 @@
       <c r="G32" s="82"/>
       <c r="H32" s="25"/>
       <c r="I32" s="90" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="J32" s="21"/>
       <c r="K32" s="19" t="s">
@@ -12592,7 +12567,7 @@
       <c r="F34" s="463"/>
       <c r="G34" s="464"/>
       <c r="H34" s="465" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="I34" s="466"/>
       <c r="J34" s="466"/>
@@ -12786,7 +12761,7 @@
         <v>95</v>
       </c>
       <c r="H46" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I46" s="89"/>
       <c r="J46" s="93"/>
@@ -12962,7 +12937,7 @@
     <row r="54" spans="1:13" ht="16.5">
       <c r="A54" s="22"/>
       <c r="B54" s="471" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C54" s="386"/>
       <c r="D54" s="386"/>
@@ -12979,7 +12954,7 @@
     <row r="55" spans="1:13" ht="34.5" customHeight="1">
       <c r="A55" s="120"/>
       <c r="B55" s="465" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C55" s="468"/>
       <c r="D55" s="468"/>
@@ -13006,7 +12981,7 @@
         <v>293</v>
       </c>
       <c r="F58" s="381" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G58" s="355"/>
       <c r="H58" s="341"/>
@@ -13055,7 +13030,7 @@
         <v>92</v>
       </c>
       <c r="B61" s="359" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C61" s="365"/>
       <c r="D61" s="365"/>
@@ -13074,7 +13049,7 @@
         <v>285</v>
       </c>
       <c r="B62" s="459" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C62" s="460"/>
       <c r="D62" s="460"/>
@@ -13189,18 +13164,18 @@
     </row>
     <row r="68" spans="1:13" ht="29.25" customHeight="1">
       <c r="A68" s="19" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B68" s="89" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C68" s="93"/>
       <c r="D68" s="91"/>
       <c r="E68" s="91" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F68" s="92" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G68" s="19"/>
       <c r="H68" s="25"/>
@@ -13215,7 +13190,7 @@
         <v>3</v>
       </c>
       <c r="B69" s="46" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C69" s="95"/>
       <c r="D69" s="96"/>
@@ -13223,7 +13198,7 @@
         <v>436</v>
       </c>
       <c r="F69" s="92" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G69" s="19"/>
       <c r="H69" s="25"/>
@@ -13251,7 +13226,7 @@
     <row r="71" spans="1:13" ht="34.5" customHeight="1">
       <c r="A71" s="22"/>
       <c r="B71" s="412" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C71" s="457"/>
       <c r="D71" s="457"/>
@@ -13339,7 +13314,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:M104"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -13431,7 +13406,7 @@
         <v>302</v>
       </c>
       <c r="B6" s="384" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C6" s="355"/>
       <c r="D6" s="355"/>
@@ -13728,7 +13703,7 @@
       <c r="G20" s="19"/>
       <c r="H20" s="338"/>
       <c r="I20" s="120" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J20" s="120"/>
       <c r="K20" s="91" t="s">
@@ -13749,14 +13724,14 @@
       <c r="G21" s="19"/>
       <c r="H21" s="338"/>
       <c r="I21" s="120" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J21" s="120"/>
       <c r="K21" s="152" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L21" s="91" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="M21" s="19"/>
     </row>
@@ -13806,7 +13781,7 @@
       <c r="G24" s="19"/>
       <c r="H24" s="338"/>
       <c r="I24" s="21" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J24" s="93"/>
       <c r="K24" s="91" t="s">
@@ -13934,7 +13909,7 @@
       <c r="G30" s="19"/>
       <c r="H30" s="338"/>
       <c r="I30" s="21" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J30" s="93"/>
       <c r="K30" s="91" t="s">
@@ -15233,7 +15208,7 @@
         <v>92</v>
       </c>
       <c r="B96" s="359" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C96" s="365"/>
       <c r="D96" s="365"/>
@@ -15251,7 +15226,7 @@
         <v>302</v>
       </c>
       <c r="B97" s="411" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C97" s="355"/>
       <c r="D97" s="355"/>
@@ -15351,7 +15326,7 @@
         <v>94</v>
       </c>
       <c r="F102" s="92" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G102" s="91" t="s">
         <v>95</v>
@@ -15375,7 +15350,7 @@
         <v>94</v>
       </c>
       <c r="F103" s="92" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G103" s="91" t="s">
         <v>95</v>
@@ -15390,7 +15365,7 @@
     <row r="104" spans="1:13" ht="30.75" customHeight="1">
       <c r="A104" s="120"/>
       <c r="B104" s="465" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C104" s="468"/>
       <c r="D104" s="468"/>
@@ -15444,7 +15419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:M193"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -15517,7 +15492,7 @@
         <v>92</v>
       </c>
       <c r="B5" s="415" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C5" s="365"/>
       <c r="D5" s="365"/>
@@ -15536,7 +15511,7 @@
         <v>302</v>
       </c>
       <c r="B6" s="384" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C6" s="355"/>
       <c r="D6" s="355"/>
@@ -15791,17 +15766,17 @@
         <v>6</v>
       </c>
       <c r="B16" s="21" t="s">
+        <v>778</v>
+      </c>
+      <c r="C16" s="107" t="s">
         <v>780</v>
-      </c>
-      <c r="C16" s="107" t="s">
-        <v>782</v>
       </c>
       <c r="D16" s="91"/>
       <c r="E16" s="95" t="s">
         <v>436</v>
       </c>
       <c r="F16" s="92" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G16" s="97" t="s">
         <v>109</v>
@@ -15971,7 +15946,7 @@
       <c r="G23" s="97"/>
       <c r="H23" s="338"/>
       <c r="I23" s="21" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="J23" s="93"/>
       <c r="K23" s="96" t="s">
@@ -15987,7 +15962,7 @@
     <row r="24" spans="1:13" ht="77.25" customHeight="1">
       <c r="A24" s="19"/>
       <c r="B24" s="400" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C24" s="389"/>
       <c r="D24" s="389"/>
@@ -15995,7 +15970,7 @@
       <c r="F24" s="389"/>
       <c r="G24" s="390"/>
       <c r="H24" s="400" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I24" s="389"/>
       <c r="J24" s="389"/>
@@ -16016,7 +15991,7 @@
         <v>293</v>
       </c>
       <c r="F27" s="381" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G27" s="355"/>
       <c r="H27" s="341"/>
@@ -16376,7 +16351,7 @@
         <v>293</v>
       </c>
       <c r="F45" s="381" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="G45" s="355"/>
       <c r="H45" s="341"/>
@@ -16395,7 +16370,7 @@
         <v>292</v>
       </c>
       <c r="F46" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G46" s="365"/>
       <c r="H46" s="366"/>
@@ -16425,7 +16400,7 @@
         <v>92</v>
       </c>
       <c r="B48" s="359" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C48" s="365"/>
       <c r="D48" s="365"/>
@@ -16444,7 +16419,7 @@
         <v>285</v>
       </c>
       <c r="B49" s="384" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C49" s="355"/>
       <c r="D49" s="355"/>
@@ -16537,17 +16512,17 @@
         <v>1</v>
       </c>
       <c r="B54" s="279" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C54" s="95" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D54" s="96"/>
       <c r="E54" s="95" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F54" s="92" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G54" s="91" t="s">
         <v>95</v>
@@ -16840,7 +16815,7 @@
       <c r="G66" s="277"/>
       <c r="H66" s="338"/>
       <c r="I66" s="21" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="J66" s="93"/>
       <c r="K66" s="96" t="s">
@@ -16856,7 +16831,7 @@
     <row r="67" spans="1:13" s="276" customFormat="1" ht="69" customHeight="1">
       <c r="A67" s="19"/>
       <c r="B67" s="400" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="C67" s="386"/>
       <c r="D67" s="386"/>
@@ -16884,7 +16859,7 @@
         <v>293</v>
       </c>
       <c r="F69" s="381" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="G69" s="355"/>
       <c r="H69" s="341"/>
@@ -16903,7 +16878,7 @@
         <v>292</v>
       </c>
       <c r="F70" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G70" s="365"/>
       <c r="H70" s="366"/>
@@ -16933,7 +16908,7 @@
         <v>92</v>
       </c>
       <c r="B72" s="359" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C72" s="365"/>
       <c r="D72" s="365"/>
@@ -17058,7 +17033,7 @@
       </c>
       <c r="H78" s="20"/>
       <c r="I78" s="21" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="J78" s="93"/>
       <c r="K78" s="96" t="s">
@@ -17131,7 +17106,7 @@
         <v>293</v>
       </c>
       <c r="F83" s="381" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="G83" s="355"/>
       <c r="H83" s="341"/>
@@ -17150,7 +17125,7 @@
         <v>292</v>
       </c>
       <c r="F84" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G84" s="365"/>
       <c r="H84" s="366"/>
@@ -17180,7 +17155,7 @@
         <v>92</v>
       </c>
       <c r="B86" s="415" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C86" s="365"/>
       <c r="D86" s="365"/>
@@ -17199,7 +17174,7 @@
         <v>285</v>
       </c>
       <c r="B87" s="384" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C87" s="355"/>
       <c r="D87" s="355"/>
@@ -17292,17 +17267,17 @@
         <v>1</v>
       </c>
       <c r="B92" s="287" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C92" s="95" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D92" s="96"/>
       <c r="E92" s="95" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F92" s="92" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G92" s="91" t="s">
         <v>95</v>
@@ -17325,17 +17300,17 @@
         <v>2</v>
       </c>
       <c r="B93" s="290" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C93" s="95" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="D93" s="96"/>
       <c r="E93" s="95" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F93" s="92" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G93" s="91" t="s">
         <v>95</v>
@@ -17358,17 +17333,17 @@
         <v>3</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C94" s="93" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="D94" s="91"/>
       <c r="E94" s="95" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F94" s="92" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G94" s="91" t="s">
         <v>415</v>
@@ -17615,7 +17590,7 @@
       <c r="G104" s="286"/>
       <c r="H104" s="473"/>
       <c r="I104" s="21" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="J104" s="93"/>
       <c r="K104" s="96" t="s">
@@ -17631,7 +17606,7 @@
     <row r="105" spans="1:13" s="284" customFormat="1" ht="69" customHeight="1">
       <c r="A105" s="19"/>
       <c r="B105" s="400" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C105" s="386"/>
       <c r="D105" s="386"/>
@@ -17659,7 +17634,7 @@
         <v>293</v>
       </c>
       <c r="F107" s="381" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G107" s="355"/>
       <c r="H107" s="341"/>
@@ -17678,7 +17653,7 @@
         <v>292</v>
       </c>
       <c r="F108" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G108" s="365"/>
       <c r="H108" s="366"/>
@@ -17708,7 +17683,7 @@
         <v>92</v>
       </c>
       <c r="B110" s="415" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C110" s="365"/>
       <c r="D110" s="365"/>
@@ -17727,7 +17702,7 @@
         <v>285</v>
       </c>
       <c r="B111" s="384" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C111" s="355"/>
       <c r="D111" s="355"/>
@@ -17820,24 +17795,24 @@
         <v>1</v>
       </c>
       <c r="B116" s="290" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C116" s="95" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D116" s="96"/>
       <c r="E116" s="95" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F116" s="92" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G116" s="91" t="s">
         <v>95</v>
       </c>
       <c r="H116" s="20"/>
       <c r="I116" s="21" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="J116" s="93"/>
       <c r="K116" s="96" t="s">
@@ -17853,17 +17828,17 @@
         <v>2</v>
       </c>
       <c r="B117" s="290" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C117" s="95" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="D117" s="96"/>
       <c r="E117" s="95" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F117" s="92" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G117" s="91" t="s">
         <v>95</v>
@@ -17880,17 +17855,17 @@
         <v>3</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C118" s="93" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="D118" s="91"/>
       <c r="E118" s="95" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F118" s="92" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G118" s="91" t="s">
         <v>415</v>
@@ -17970,7 +17945,7 @@
         <v>293</v>
       </c>
       <c r="F122" s="381" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G122" s="355"/>
       <c r="H122" s="341"/>
@@ -17989,7 +17964,7 @@
         <v>292</v>
       </c>
       <c r="F123" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G123" s="365"/>
       <c r="H123" s="366"/>
@@ -18019,7 +17994,7 @@
         <v>92</v>
       </c>
       <c r="B125" s="415" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C125" s="365"/>
       <c r="D125" s="365"/>
@@ -18038,7 +18013,7 @@
         <v>285</v>
       </c>
       <c r="B126" s="384" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C126" s="355"/>
       <c r="D126" s="355"/>
@@ -18261,17 +18236,17 @@
         <v>6</v>
       </c>
       <c r="B135" s="21" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C135" s="107" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="D135" s="91"/>
       <c r="E135" s="95" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F135" s="92" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G135" s="321" t="s">
         <v>109</v>
@@ -18441,7 +18416,7 @@
       <c r="G142" s="321"/>
       <c r="H142" s="338"/>
       <c r="I142" s="21" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="J142" s="93"/>
       <c r="K142" s="96" t="s">
@@ -18457,7 +18432,7 @@
     <row r="143" spans="1:13" s="317" customFormat="1" ht="48.75" customHeight="1">
       <c r="A143" s="19"/>
       <c r="B143" s="400" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C143" s="389"/>
       <c r="D143" s="389"/>
@@ -18485,7 +18460,7 @@
         <v>293</v>
       </c>
       <c r="F145" s="381" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="G145" s="355"/>
       <c r="H145" s="341"/>
@@ -18534,7 +18509,7 @@
         <v>92</v>
       </c>
       <c r="B148" s="359" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C148" s="365"/>
       <c r="D148" s="365"/>
@@ -18658,7 +18633,7 @@
         <v>95</v>
       </c>
       <c r="H154" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I154" s="21"/>
       <c r="J154" s="93"/>
@@ -18747,7 +18722,7 @@
         <v>293</v>
       </c>
       <c r="F160" s="381" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G160" s="355"/>
       <c r="H160" s="341"/>
@@ -18921,7 +18896,7 @@
         <v>95</v>
       </c>
       <c r="H169" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I169" s="21"/>
       <c r="J169" s="93"/>
@@ -19067,7 +19042,7 @@
         <v>293</v>
       </c>
       <c r="F178" s="381" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G178" s="355"/>
       <c r="H178" s="341"/>
@@ -19116,7 +19091,7 @@
         <v>92</v>
       </c>
       <c r="B181" s="359" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C181" s="365"/>
       <c r="D181" s="365"/>
@@ -19505,7 +19480,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:M31"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -19595,7 +19570,7 @@
         <v>302</v>
       </c>
       <c r="B6" s="411" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C6" s="355"/>
       <c r="D6" s="355"/>
@@ -19702,7 +19677,7 @@
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="21" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="J11" s="93"/>
       <c r="K11" s="96" t="s">
@@ -19725,7 +19700,7 @@
       <c r="G12" s="91"/>
       <c r="H12" s="95"/>
       <c r="I12" s="21" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="J12" s="93"/>
       <c r="K12" s="96" t="s">
@@ -19748,7 +19723,7 @@
       <c r="G13" s="91"/>
       <c r="H13" s="93"/>
       <c r="I13" s="21" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="J13" s="93"/>
       <c r="K13" s="96" t="s">
@@ -19771,7 +19746,7 @@
       <c r="G14" s="97"/>
       <c r="H14" s="93"/>
       <c r="I14" s="21" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="J14" s="93"/>
       <c r="K14" s="96" t="s">
@@ -19794,7 +19769,7 @@
       <c r="G15" s="97"/>
       <c r="H15" s="93"/>
       <c r="I15" s="21" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="J15" s="93"/>
       <c r="K15" s="96" t="s">
@@ -19817,7 +19792,7 @@
       <c r="G16" s="97"/>
       <c r="H16" s="93"/>
       <c r="I16" s="21" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="J16" s="93"/>
       <c r="K16" s="96" t="s">
@@ -19840,7 +19815,7 @@
       <c r="G17" s="97"/>
       <c r="H17" s="19"/>
       <c r="I17" s="21" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="J17" s="93"/>
       <c r="K17" s="96" t="s">
@@ -19861,7 +19836,7 @@
       <c r="G18" s="97"/>
       <c r="H18" s="19"/>
       <c r="I18" s="21" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="J18" s="93"/>
       <c r="K18" s="96" t="s">
@@ -19882,7 +19857,7 @@
       <c r="G19" s="97"/>
       <c r="H19" s="19"/>
       <c r="I19" s="21" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="J19" s="93"/>
       <c r="K19" s="96" t="s">
@@ -19903,7 +19878,7 @@
       <c r="G20" s="97"/>
       <c r="H20" s="19"/>
       <c r="I20" s="21" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="J20" s="93"/>
       <c r="K20" s="96" t="s">
@@ -19924,7 +19899,7 @@
       <c r="G21" s="97"/>
       <c r="H21" s="19"/>
       <c r="I21" s="21" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="J21" s="93"/>
       <c r="K21" s="96" t="s">
@@ -19945,7 +19920,7 @@
       <c r="G22" s="97"/>
       <c r="H22" s="19"/>
       <c r="I22" s="21" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="J22" s="93"/>
       <c r="K22" s="96" t="s">
@@ -19966,7 +19941,7 @@
       <c r="G23" s="97"/>
       <c r="H23" s="19"/>
       <c r="I23" s="21" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="J23" s="93"/>
       <c r="K23" s="96" t="s">
@@ -19987,7 +19962,7 @@
       <c r="G24" s="97"/>
       <c r="H24" s="19"/>
       <c r="I24" s="21" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="J24" s="93"/>
       <c r="K24" s="96" t="s">
@@ -20008,7 +19983,7 @@
       <c r="G25" s="97"/>
       <c r="H25" s="19"/>
       <c r="I25" s="21" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="J25" s="93"/>
       <c r="K25" s="96" t="s">
@@ -20029,7 +20004,7 @@
       <c r="G26" s="97"/>
       <c r="H26" s="19"/>
       <c r="I26" s="21" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="J26" s="93"/>
       <c r="K26" s="96" t="s">
@@ -20050,7 +20025,7 @@
       <c r="G27" s="97"/>
       <c r="H27" s="19"/>
       <c r="I27" s="21" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="J27" s="93"/>
       <c r="K27" s="96" t="s">
@@ -20071,7 +20046,7 @@
       <c r="G28" s="97"/>
       <c r="H28" s="19"/>
       <c r="I28" s="21" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="J28" s="93"/>
       <c r="K28" s="96" t="s">
@@ -20092,7 +20067,7 @@
       <c r="G29" s="97"/>
       <c r="H29" s="19"/>
       <c r="I29" s="21" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J29" s="93"/>
       <c r="K29" s="96" t="s">
@@ -20113,7 +20088,7 @@
       <c r="G30" s="97"/>
       <c r="H30" s="19"/>
       <c r="I30" s="21" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="J30" s="93"/>
       <c r="K30" s="96" t="s">
@@ -20162,7 +20137,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:M51"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -20560,7 +20535,7 @@
         <v>302</v>
       </c>
       <c r="B25" s="384" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C25" s="355"/>
       <c r="D25" s="355"/>
@@ -20870,7 +20845,7 @@
         <v>302</v>
       </c>
       <c r="B44" s="384" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C44" s="355"/>
       <c r="D44" s="355"/>
@@ -20977,7 +20952,7 @@
       </c>
       <c r="H49" s="26"/>
       <c r="I49" s="46" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J49" s="95"/>
       <c r="K49" s="96" t="s">
@@ -21015,7 +20990,7 @@
       <c r="G51" s="22"/>
       <c r="H51" s="20"/>
       <c r="I51" s="21" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="J51" s="21"/>
       <c r="K51" s="19"/>
@@ -21073,7 +21048,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2190574F-8459-4AA2-84BD-26A8AA46B8F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M93"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -21100,7 +21075,7 @@
         <v>294</v>
       </c>
       <c r="B2" s="380" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C2" s="355"/>
       <c r="D2" s="341"/>
@@ -21108,7 +21083,7 @@
         <v>293</v>
       </c>
       <c r="F2" s="381" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G2" s="355"/>
       <c r="H2" s="341"/>
@@ -21127,7 +21102,7 @@
         <v>292</v>
       </c>
       <c r="F3" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G3" s="365"/>
       <c r="H3" s="366"/>
@@ -21157,7 +21132,7 @@
         <v>92</v>
       </c>
       <c r="B5" s="359" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C5" s="365"/>
       <c r="D5" s="365"/>
@@ -21176,7 +21151,7 @@
         <v>285</v>
       </c>
       <c r="B6" s="384" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C6" s="355"/>
       <c r="D6" s="355"/>
@@ -21284,7 +21259,7 @@
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="21" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="J11" s="93"/>
       <c r="K11" s="91" t="s">
@@ -21294,7 +21269,7 @@
         <v>437</v>
       </c>
       <c r="M11" s="92" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -21307,7 +21282,7 @@
       <c r="G12" s="91"/>
       <c r="H12" s="176"/>
       <c r="I12" s="46" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="J12" s="95"/>
       <c r="K12" s="96"/>
@@ -21324,7 +21299,7 @@
       <c r="G13" s="19"/>
       <c r="H13" s="94"/>
       <c r="I13" s="46" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J13" s="95"/>
       <c r="K13" s="96"/>
@@ -21355,7 +21330,7 @@
       <c r="F15" s="463"/>
       <c r="G15" s="464"/>
       <c r="H15" s="470" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I15" s="466"/>
       <c r="J15" s="466"/>
@@ -21368,7 +21343,7 @@
         <v>294</v>
       </c>
       <c r="B17" s="380" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C17" s="355"/>
       <c r="D17" s="341"/>
@@ -21376,7 +21351,7 @@
         <v>293</v>
       </c>
       <c r="F17" s="381" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="G17" s="355"/>
       <c r="H17" s="341"/>
@@ -21395,7 +21370,7 @@
         <v>292</v>
       </c>
       <c r="F18" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G18" s="365"/>
       <c r="H18" s="366"/>
@@ -21425,7 +21400,7 @@
         <v>92</v>
       </c>
       <c r="B20" s="359" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C20" s="365"/>
       <c r="D20" s="365"/>
@@ -21444,7 +21419,7 @@
         <v>285</v>
       </c>
       <c r="B21" s="384" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C21" s="355"/>
       <c r="D21" s="355"/>
@@ -21562,7 +21537,7 @@
         <v>214</v>
       </c>
       <c r="M26" s="92" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="31.5" customHeight="1">
@@ -21612,7 +21587,7 @@
       <c r="F29" s="463"/>
       <c r="G29" s="464"/>
       <c r="H29" s="470" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="I29" s="466"/>
       <c r="J29" s="466"/>
@@ -21640,7 +21615,7 @@
         <v>294</v>
       </c>
       <c r="B31" s="380" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C31" s="355"/>
       <c r="D31" s="341"/>
@@ -21648,7 +21623,7 @@
         <v>293</v>
       </c>
       <c r="F31" s="381" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G31" s="355"/>
       <c r="H31" s="341"/>
@@ -21667,7 +21642,7 @@
         <v>292</v>
       </c>
       <c r="F32" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G32" s="365"/>
       <c r="H32" s="366"/>
@@ -21697,7 +21672,7 @@
         <v>92</v>
       </c>
       <c r="B34" s="359" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C34" s="365"/>
       <c r="D34" s="365"/>
@@ -21716,7 +21691,7 @@
         <v>285</v>
       </c>
       <c r="B35" s="384" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C35" s="355"/>
       <c r="D35" s="355"/>
@@ -21842,7 +21817,7 @@
         <v>2</v>
       </c>
       <c r="B41" s="93" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C41" s="45"/>
       <c r="D41" s="21"/>
@@ -21850,24 +21825,24 @@
         <v>436</v>
       </c>
       <c r="F41" s="92" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G41" s="91" t="s">
         <v>95</v>
       </c>
       <c r="H41" s="94"/>
       <c r="I41" s="46" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="J41" s="95"/>
       <c r="K41" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L41" s="96" t="s">
         <v>99</v>
       </c>
       <c r="M41" s="119" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -21894,7 +21869,7 @@
       <c r="F43" s="463"/>
       <c r="G43" s="464"/>
       <c r="H43" s="465" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="I43" s="466"/>
       <c r="J43" s="466"/>
@@ -21907,7 +21882,7 @@
         <v>294</v>
       </c>
       <c r="B45" s="380" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C45" s="405"/>
       <c r="D45" s="406"/>
@@ -21915,7 +21890,7 @@
         <v>293</v>
       </c>
       <c r="F45" s="381" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G45" s="481"/>
       <c r="H45" s="482"/>
@@ -21934,7 +21909,7 @@
         <v>292</v>
       </c>
       <c r="F46" s="381" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G46" s="481"/>
       <c r="H46" s="482"/>
@@ -21945,7 +21920,7 @@
         <v>90</v>
       </c>
       <c r="B47" s="379" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C47" s="483"/>
       <c r="D47" s="483"/>
@@ -21964,7 +21939,7 @@
         <v>92</v>
       </c>
       <c r="B48" s="342" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C48" s="357"/>
       <c r="D48" s="357"/>
@@ -22147,7 +22122,7 @@
         <v>294</v>
       </c>
       <c r="B59" s="380" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C59" s="355"/>
       <c r="D59" s="341"/>
@@ -22155,7 +22130,7 @@
         <v>293</v>
       </c>
       <c r="F59" s="381" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G59" s="355"/>
       <c r="H59" s="341"/>
@@ -22174,7 +22149,7 @@
         <v>292</v>
       </c>
       <c r="F60" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G60" s="365"/>
       <c r="H60" s="366"/>
@@ -22185,7 +22160,7 @@
         <v>90</v>
       </c>
       <c r="B61" s="379" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C61" s="355"/>
       <c r="D61" s="355"/>
@@ -22204,7 +22179,7 @@
         <v>92</v>
       </c>
       <c r="B62" s="359" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C62" s="365"/>
       <c r="D62" s="365"/>
@@ -22223,7 +22198,7 @@
         <v>285</v>
       </c>
       <c r="B63" s="384" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C63" s="355"/>
       <c r="D63" s="355"/>
@@ -22326,7 +22301,7 @@
         <v>428</v>
       </c>
       <c r="G68" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H68" s="26"/>
       <c r="I68" s="21"/>
@@ -22340,7 +22315,7 @@
         <v>2</v>
       </c>
       <c r="B69" s="46" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C69" s="95"/>
       <c r="D69" s="96"/>
@@ -22348,10 +22323,10 @@
         <v>436</v>
       </c>
       <c r="F69" s="92" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G69" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H69" s="95"/>
       <c r="I69" s="21"/>
@@ -22448,7 +22423,7 @@
     <row r="75" spans="1:13" ht="28.5" customHeight="1">
       <c r="A75" s="19"/>
       <c r="B75" s="385" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C75" s="386"/>
       <c r="D75" s="386"/>
@@ -22467,7 +22442,7 @@
         <v>294</v>
       </c>
       <c r="B77" s="380" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C77" s="355"/>
       <c r="D77" s="341"/>
@@ -22475,7 +22450,7 @@
         <v>293</v>
       </c>
       <c r="F77" s="381" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="G77" s="355"/>
       <c r="H77" s="341"/>
@@ -22494,7 +22469,7 @@
         <v>292</v>
       </c>
       <c r="F78" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G78" s="365"/>
       <c r="H78" s="366"/>
@@ -22505,7 +22480,7 @@
         <v>90</v>
       </c>
       <c r="B79" s="379" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C79" s="355"/>
       <c r="D79" s="355"/>
@@ -22524,7 +22499,7 @@
         <v>92</v>
       </c>
       <c r="B80" s="359" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C80" s="365"/>
       <c r="D80" s="365"/>
@@ -22543,7 +22518,7 @@
         <v>285</v>
       </c>
       <c r="B81" s="384" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C81" s="355"/>
       <c r="D81" s="355"/>
@@ -22660,7 +22635,7 @@
         <v>2</v>
       </c>
       <c r="B87" s="46" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C87" s="95"/>
       <c r="D87" s="96"/>
@@ -22668,7 +22643,7 @@
         <v>436</v>
       </c>
       <c r="F87" s="92" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G87" s="91" t="s">
         <v>95</v>
@@ -22685,7 +22660,7 @@
         <v>3</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C88" s="93"/>
       <c r="D88" s="91"/>
@@ -22693,7 +22668,7 @@
         <v>436</v>
       </c>
       <c r="F88" s="92" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G88" s="91" t="s">
         <v>95</v>
@@ -22776,7 +22751,7 @@
     <row r="93" spans="1:13" ht="29.25" customHeight="1">
       <c r="A93" s="19"/>
       <c r="B93" s="400" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C93" s="389"/>
       <c r="D93" s="389"/>
@@ -22892,7 +22867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6812824E-2709-41F4-AEF8-2C184ED6FD04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M93"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -22919,7 +22894,7 @@
         <v>294</v>
       </c>
       <c r="B2" s="380" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C2" s="355"/>
       <c r="D2" s="341"/>
@@ -22927,7 +22902,7 @@
         <v>293</v>
       </c>
       <c r="F2" s="381" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G2" s="355"/>
       <c r="H2" s="341"/>
@@ -22946,7 +22921,7 @@
         <v>292</v>
       </c>
       <c r="F3" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G3" s="365"/>
       <c r="H3" s="366"/>
@@ -22976,7 +22951,7 @@
         <v>92</v>
       </c>
       <c r="B5" s="415" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C5" s="365"/>
       <c r="D5" s="365"/>
@@ -22995,7 +22970,7 @@
         <v>285</v>
       </c>
       <c r="B6" s="384" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C6" s="355"/>
       <c r="D6" s="355"/>
@@ -23103,7 +23078,7 @@
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="21" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="J11" s="93"/>
       <c r="K11" s="91" t="s">
@@ -23113,7 +23088,7 @@
         <v>437</v>
       </c>
       <c r="M11" s="92" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -23126,7 +23101,7 @@
       <c r="G12" s="91"/>
       <c r="H12" s="176"/>
       <c r="I12" s="304" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="J12" s="95"/>
       <c r="K12" s="96"/>
@@ -23143,7 +23118,7 @@
       <c r="G13" s="19"/>
       <c r="H13" s="94"/>
       <c r="I13" s="304" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J13" s="95"/>
       <c r="K13" s="96"/>
@@ -23174,7 +23149,7 @@
       <c r="F15" s="463"/>
       <c r="G15" s="464"/>
       <c r="H15" s="470" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I15" s="466"/>
       <c r="J15" s="466"/>
@@ -23187,7 +23162,7 @@
         <v>294</v>
       </c>
       <c r="B17" s="380" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C17" s="355"/>
       <c r="D17" s="341"/>
@@ -23195,7 +23170,7 @@
         <v>293</v>
       </c>
       <c r="F17" s="381" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="G17" s="355"/>
       <c r="H17" s="341"/>
@@ -23214,7 +23189,7 @@
         <v>292</v>
       </c>
       <c r="F18" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G18" s="365"/>
       <c r="H18" s="366"/>
@@ -23244,7 +23219,7 @@
         <v>92</v>
       </c>
       <c r="B20" s="492" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C20" s="365"/>
       <c r="D20" s="365"/>
@@ -23263,7 +23238,7 @@
         <v>285</v>
       </c>
       <c r="B21" s="384" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C21" s="355"/>
       <c r="D21" s="355"/>
@@ -23381,7 +23356,7 @@
         <v>214</v>
       </c>
       <c r="M26" s="92" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="31.5" customHeight="1">
@@ -23431,7 +23406,7 @@
       <c r="F29" s="463"/>
       <c r="G29" s="464"/>
       <c r="H29" s="470" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="I29" s="466"/>
       <c r="J29" s="466"/>
@@ -23459,7 +23434,7 @@
         <v>294</v>
       </c>
       <c r="B31" s="380" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C31" s="355"/>
       <c r="D31" s="341"/>
@@ -23467,7 +23442,7 @@
         <v>293</v>
       </c>
       <c r="F31" s="381" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G31" s="355"/>
       <c r="H31" s="341"/>
@@ -23486,7 +23461,7 @@
         <v>292</v>
       </c>
       <c r="F32" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G32" s="365"/>
       <c r="H32" s="366"/>
@@ -23516,7 +23491,7 @@
         <v>92</v>
       </c>
       <c r="B34" s="492" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C34" s="365"/>
       <c r="D34" s="365"/>
@@ -23535,7 +23510,7 @@
         <v>285</v>
       </c>
       <c r="B35" s="384" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C35" s="355"/>
       <c r="D35" s="355"/>
@@ -23661,7 +23636,7 @@
         <v>2</v>
       </c>
       <c r="B41" s="93" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C41" s="303"/>
       <c r="D41" s="21"/>
@@ -23669,24 +23644,24 @@
         <v>436</v>
       </c>
       <c r="F41" s="92" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G41" s="91" t="s">
         <v>95</v>
       </c>
       <c r="H41" s="94"/>
       <c r="I41" s="304" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="J41" s="95"/>
       <c r="K41" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L41" s="96" t="s">
         <v>99</v>
       </c>
       <c r="M41" s="119" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -23713,7 +23688,7 @@
       <c r="F43" s="463"/>
       <c r="G43" s="464"/>
       <c r="H43" s="465" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="I43" s="466"/>
       <c r="J43" s="466"/>
@@ -23726,7 +23701,7 @@
         <v>294</v>
       </c>
       <c r="B45" s="380" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C45" s="405"/>
       <c r="D45" s="406"/>
@@ -23734,7 +23709,7 @@
         <v>293</v>
       </c>
       <c r="F45" s="381" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G45" s="481"/>
       <c r="H45" s="482"/>
@@ -23753,7 +23728,7 @@
         <v>292</v>
       </c>
       <c r="F46" s="381" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G46" s="481"/>
       <c r="H46" s="482"/>
@@ -23764,7 +23739,7 @@
         <v>90</v>
       </c>
       <c r="B47" s="379" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C47" s="483"/>
       <c r="D47" s="483"/>
@@ -23783,7 +23758,7 @@
         <v>92</v>
       </c>
       <c r="B48" s="491" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C48" s="357"/>
       <c r="D48" s="357"/>
@@ -23966,7 +23941,7 @@
         <v>294</v>
       </c>
       <c r="B59" s="380" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C59" s="355"/>
       <c r="D59" s="341"/>
@@ -23974,7 +23949,7 @@
         <v>293</v>
       </c>
       <c r="F59" s="381" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G59" s="355"/>
       <c r="H59" s="341"/>
@@ -23993,7 +23968,7 @@
         <v>292</v>
       </c>
       <c r="F60" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G60" s="365"/>
       <c r="H60" s="366"/>
@@ -24004,7 +23979,7 @@
         <v>90</v>
       </c>
       <c r="B61" s="379" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C61" s="355"/>
       <c r="D61" s="355"/>
@@ -24023,7 +23998,7 @@
         <v>92</v>
       </c>
       <c r="B62" s="415" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C62" s="365"/>
       <c r="D62" s="365"/>
@@ -24042,7 +24017,7 @@
         <v>285</v>
       </c>
       <c r="B63" s="384" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C63" s="355"/>
       <c r="D63" s="355"/>
@@ -24145,7 +24120,7 @@
         <v>428</v>
       </c>
       <c r="G68" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H68" s="26"/>
       <c r="I68" s="21"/>
@@ -24159,7 +24134,7 @@
         <v>2</v>
       </c>
       <c r="B69" s="304" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C69" s="95"/>
       <c r="D69" s="96"/>
@@ -24167,10 +24142,10 @@
         <v>436</v>
       </c>
       <c r="F69" s="92" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G69" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H69" s="95"/>
       <c r="I69" s="21"/>
@@ -24267,7 +24242,7 @@
     <row r="75" spans="1:13" ht="28.5" customHeight="1">
       <c r="A75" s="19"/>
       <c r="B75" s="385" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C75" s="386"/>
       <c r="D75" s="386"/>
@@ -24286,7 +24261,7 @@
         <v>294</v>
       </c>
       <c r="B77" s="380" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C77" s="355"/>
       <c r="D77" s="341"/>
@@ -24294,7 +24269,7 @@
         <v>293</v>
       </c>
       <c r="F77" s="381" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="G77" s="355"/>
       <c r="H77" s="341"/>
@@ -24313,7 +24288,7 @@
         <v>292</v>
       </c>
       <c r="F78" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G78" s="365"/>
       <c r="H78" s="366"/>
@@ -24324,7 +24299,7 @@
         <v>90</v>
       </c>
       <c r="B79" s="379" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C79" s="355"/>
       <c r="D79" s="355"/>
@@ -24343,7 +24318,7 @@
         <v>92</v>
       </c>
       <c r="B80" s="415" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C80" s="365"/>
       <c r="D80" s="365"/>
@@ -24362,7 +24337,7 @@
         <v>285</v>
       </c>
       <c r="B81" s="384" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C81" s="355"/>
       <c r="D81" s="355"/>
@@ -24479,7 +24454,7 @@
         <v>2</v>
       </c>
       <c r="B87" s="304" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C87" s="95"/>
       <c r="D87" s="96"/>
@@ -24487,7 +24462,7 @@
         <v>436</v>
       </c>
       <c r="F87" s="92" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G87" s="91" t="s">
         <v>95</v>
@@ -24504,7 +24479,7 @@
         <v>3</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C88" s="93"/>
       <c r="D88" s="91"/>
@@ -24512,7 +24487,7 @@
         <v>436</v>
       </c>
       <c r="F88" s="92" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G88" s="91" t="s">
         <v>95</v>
@@ -24595,7 +24570,7 @@
     <row r="93" spans="1:13" ht="29.25" customHeight="1">
       <c r="A93" s="19"/>
       <c r="B93" s="400" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C93" s="389"/>
       <c r="D93" s="389"/>
@@ -24711,7 +24686,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:M134"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -24723,7 +24698,7 @@
         <v>294</v>
       </c>
       <c r="B2" s="380" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C2" s="355"/>
       <c r="D2" s="341"/>
@@ -24731,7 +24706,7 @@
         <v>293</v>
       </c>
       <c r="F2" s="381" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G2" s="355"/>
       <c r="H2" s="341"/>
@@ -24799,7 +24774,7 @@
         <v>302</v>
       </c>
       <c r="B6" s="411" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C6" s="355"/>
       <c r="D6" s="355"/>
@@ -25003,7 +24978,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C15" s="93"/>
       <c r="D15" s="91"/>
@@ -25028,7 +25003,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C16" s="93"/>
       <c r="D16" s="91"/>
@@ -25053,7 +25028,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C17" s="93"/>
       <c r="D17" s="91"/>
@@ -25078,12 +25053,12 @@
         <v>8</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C18" s="21"/>
       <c r="D18" s="21"/>
       <c r="E18" s="21" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F18" s="92" t="s">
         <v>99</v>
@@ -25103,12 +25078,12 @@
         <v>9</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C19" s="93"/>
       <c r="D19" s="91"/>
       <c r="E19" s="89" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F19" s="92" t="s">
         <v>99</v>
@@ -25128,12 +25103,12 @@
         <v>10</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C20" s="93"/>
       <c r="D20" s="91"/>
       <c r="E20" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F20" s="92" t="s">
         <v>99</v>
@@ -25153,12 +25128,12 @@
         <v>11</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C21" s="93"/>
       <c r="D21" s="91"/>
       <c r="E21" s="89" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F21" s="92" t="s">
         <v>99</v>
@@ -25178,12 +25153,12 @@
         <v>12</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C22" s="93"/>
       <c r="D22" s="91"/>
       <c r="E22" s="89" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F22" s="92" t="s">
         <v>99</v>
@@ -25203,12 +25178,12 @@
         <v>13</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C23" s="93"/>
       <c r="D23" s="91"/>
       <c r="E23" s="89" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F23" s="92" t="s">
         <v>99</v>
@@ -25226,7 +25201,7 @@
     <row r="24" spans="1:13" ht="87.75" customHeight="1">
       <c r="A24" s="22"/>
       <c r="B24" s="400" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C24" s="386"/>
       <c r="D24" s="386"/>
@@ -25235,7 +25210,7 @@
       <c r="G24" s="387"/>
       <c r="H24" s="20"/>
       <c r="I24" s="25" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J24" s="21"/>
       <c r="K24" s="19"/>
@@ -25247,7 +25222,7 @@
         <v>294</v>
       </c>
       <c r="B27" s="380" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C27" s="355"/>
       <c r="D27" s="341"/>
@@ -25255,7 +25230,7 @@
         <v>293</v>
       </c>
       <c r="F27" s="381" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G27" s="355"/>
       <c r="H27" s="341"/>
@@ -25304,7 +25279,7 @@
         <v>92</v>
       </c>
       <c r="B30" s="359" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C30" s="365"/>
       <c r="D30" s="365"/>
@@ -25323,7 +25298,7 @@
         <v>285</v>
       </c>
       <c r="B31" s="411" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C31" s="355"/>
       <c r="D31" s="355"/>
@@ -25500,7 +25475,7 @@
         <v>294</v>
       </c>
       <c r="B43" s="380" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C43" s="355"/>
       <c r="D43" s="341"/>
@@ -25508,7 +25483,7 @@
         <v>293</v>
       </c>
       <c r="F43" s="381" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G43" s="355"/>
       <c r="H43" s="341"/>
@@ -25538,7 +25513,7 @@
         <v>90</v>
       </c>
       <c r="B45" s="379" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C45" s="355"/>
       <c r="D45" s="355"/>
@@ -25557,7 +25532,7 @@
         <v>92</v>
       </c>
       <c r="B46" s="359" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C46" s="365"/>
       <c r="D46" s="365"/>
@@ -25681,7 +25656,7 @@
       </c>
       <c r="H52" s="26"/>
       <c r="I52" s="46" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J52" s="95"/>
       <c r="K52" s="96" t="s">
@@ -25747,7 +25722,7 @@
       <c r="G56" s="54"/>
       <c r="H56" s="49"/>
       <c r="I56" s="25" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="J56" s="21"/>
       <c r="K56" s="19"/>
@@ -25759,7 +25734,7 @@
         <v>294</v>
       </c>
       <c r="B59" s="380" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C59" s="355"/>
       <c r="D59" s="341"/>
@@ -25767,7 +25742,7 @@
         <v>293</v>
       </c>
       <c r="F59" s="381" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G59" s="355"/>
       <c r="H59" s="341"/>
@@ -25797,7 +25772,7 @@
         <v>90</v>
       </c>
       <c r="B61" s="379" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C61" s="355"/>
       <c r="D61" s="355"/>
@@ -25816,7 +25791,7 @@
         <v>92</v>
       </c>
       <c r="B62" s="359" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C62" s="365"/>
       <c r="D62" s="365"/>
@@ -26010,7 +25985,7 @@
         <v>294</v>
       </c>
       <c r="B75" s="380" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C75" s="355"/>
       <c r="D75" s="341"/>
@@ -26018,7 +25993,7 @@
         <v>293</v>
       </c>
       <c r="F75" s="381" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G75" s="355"/>
       <c r="H75" s="341"/>
@@ -26048,7 +26023,7 @@
         <v>90</v>
       </c>
       <c r="B77" s="379" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C77" s="355"/>
       <c r="D77" s="355"/>
@@ -26067,7 +26042,7 @@
         <v>92</v>
       </c>
       <c r="B78" s="359" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C78" s="365"/>
       <c r="D78" s="365"/>
@@ -26086,7 +26061,7 @@
         <v>285</v>
       </c>
       <c r="B79" s="411" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C79" s="355"/>
       <c r="D79" s="355"/>
@@ -26273,7 +26248,7 @@
         <v>294</v>
       </c>
       <c r="B91" s="380" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C91" s="355"/>
       <c r="D91" s="341"/>
@@ -26281,7 +26256,7 @@
         <v>293</v>
       </c>
       <c r="F91" s="381" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G91" s="355"/>
       <c r="H91" s="341"/>
@@ -26311,7 +26286,7 @@
         <v>90</v>
       </c>
       <c r="B93" s="379" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C93" s="355"/>
       <c r="D93" s="355"/>
@@ -26330,7 +26305,7 @@
         <v>92</v>
       </c>
       <c r="B94" s="359" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C94" s="365"/>
       <c r="D94" s="365"/>
@@ -26349,7 +26324,7 @@
         <v>285</v>
       </c>
       <c r="B95" s="411" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C95" s="355"/>
       <c r="D95" s="355"/>
@@ -26541,7 +26516,7 @@
         <v>294</v>
       </c>
       <c r="B106" s="380" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C106" s="355"/>
       <c r="D106" s="341"/>
@@ -26549,7 +26524,7 @@
         <v>293</v>
       </c>
       <c r="F106" s="381" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="G106" s="355"/>
       <c r="H106" s="341"/>
@@ -26579,7 +26554,7 @@
         <v>90</v>
       </c>
       <c r="B108" s="379" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C108" s="355"/>
       <c r="D108" s="355"/>
@@ -26598,7 +26573,7 @@
         <v>92</v>
       </c>
       <c r="B109" s="359" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C109" s="365"/>
       <c r="D109" s="365"/>
@@ -26617,7 +26592,7 @@
         <v>285</v>
       </c>
       <c r="B110" s="384" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C110" s="355"/>
       <c r="D110" s="355"/>
@@ -26735,7 +26710,7 @@
         <v>2</v>
       </c>
       <c r="B116" s="21" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C116" s="93"/>
       <c r="D116" s="91"/>
@@ -26743,7 +26718,7 @@
         <v>436</v>
       </c>
       <c r="F116" s="92" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G116" s="91" t="s">
         <v>95</v>
@@ -26805,7 +26780,7 @@
         <v>294</v>
       </c>
       <c r="B121" s="380" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C121" s="355"/>
       <c r="D121" s="341"/>
@@ -26813,7 +26788,7 @@
         <v>293</v>
       </c>
       <c r="F121" s="381" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="G121" s="355"/>
       <c r="H121" s="341"/>
@@ -26862,7 +26837,7 @@
         <v>92</v>
       </c>
       <c r="B124" s="359" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C124" s="365"/>
       <c r="D124" s="365"/>
@@ -26881,7 +26856,7 @@
         <v>285</v>
       </c>
       <c r="B125" s="384" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C125" s="355"/>
       <c r="D125" s="355"/>
@@ -26989,7 +26964,7 @@
       </c>
       <c r="H130" s="26"/>
       <c r="I130" s="263" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="J130" s="95"/>
       <c r="K130" s="96" t="s">
@@ -27055,7 +27030,7 @@
       <c r="G134" s="54"/>
       <c r="H134" s="49"/>
       <c r="I134" s="25" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="J134" s="21"/>
       <c r="K134" s="19"/>
@@ -27184,7 +27159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -27232,7 +27207,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="340" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="D3" s="341"/>
       <c r="E3" s="88"/>
@@ -27832,7 +27807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76D5090-A6DA-4661-86AC-11F08FA0E640}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:O94"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -27862,7 +27837,7 @@
   <sheetData>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="329" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B2" s="329"/>
       <c r="C2" s="329"/>
@@ -27874,7 +27849,7 @@
       </c>
       <c r="B3" s="534"/>
       <c r="C3" s="527" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D3" s="527"/>
     </row>
@@ -27890,7 +27865,7 @@
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
       <c r="A5" s="533" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B5" s="534"/>
       <c r="C5" s="527"/>
@@ -27898,7 +27873,7 @@
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
       <c r="A6" s="533" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B6" s="534"/>
       <c r="C6" s="527"/>
@@ -27906,17 +27881,17 @@
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
       <c r="A7" s="533" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B7" s="534"/>
       <c r="C7" s="527" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D7" s="527"/>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
       <c r="A8" s="533" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B8" s="534"/>
       <c r="C8" s="527"/>
@@ -27924,7 +27899,7 @@
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
       <c r="A9" s="536" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B9" s="537"/>
       <c r="C9" s="527"/>
@@ -27932,11 +27907,11 @@
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
       <c r="A10" s="533" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B10" s="534"/>
       <c r="C10" s="535" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D10" s="527"/>
     </row>
@@ -27946,7 +27921,7 @@
     </row>
     <row r="13" spans="1:13" ht="16.5" customHeight="1">
       <c r="A13" s="531" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B13" s="532"/>
       <c r="C13" s="532"/>
@@ -27964,15 +27939,15 @@
         <v>305</v>
       </c>
       <c r="B15" s="498" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C15" s="499"/>
       <c r="D15" s="500"/>
       <c r="E15" s="57" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F15" s="501" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G15" s="502"/>
       <c r="H15" s="503"/>
@@ -28002,7 +27977,7 @@
         <v>92</v>
       </c>
       <c r="B17" s="505" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C17" s="506"/>
       <c r="D17" s="506"/>
@@ -28011,7 +27986,7 @@
       <c r="G17" s="506"/>
       <c r="H17" s="507"/>
       <c r="I17" s="156" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="J17" s="156"/>
       <c r="K17" s="156"/>
@@ -28020,10 +27995,10 @@
     </row>
     <row r="18" spans="1:15" ht="81" customHeight="1">
       <c r="A18" s="60" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B18" s="508" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C18" s="502"/>
       <c r="D18" s="502"/>
@@ -28043,7 +28018,7 @@
         <v>301</v>
       </c>
       <c r="B20" s="517" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C20" s="502"/>
       <c r="D20" s="502"/>
@@ -28051,7 +28026,7 @@
       <c r="F20" s="502"/>
       <c r="G20" s="503"/>
       <c r="H20" s="518" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="I20" s="502"/>
       <c r="J20" s="502"/>
@@ -28109,7 +28084,7 @@
         <v>309</v>
       </c>
       <c r="L22" s="64" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="M22" s="63" t="s">
         <v>285</v>
@@ -28121,30 +28096,30 @@
         <v>1</v>
       </c>
       <c r="B23" s="509" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C23" s="510"/>
       <c r="D23" s="159" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E23" s="160" t="s">
         <v>94</v>
       </c>
       <c r="F23" s="161" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G23" s="160" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H23" s="67"/>
       <c r="I23" s="68" t="s">
+        <v>553</v>
+      </c>
+      <c r="J23" s="162" t="s">
+        <v>554</v>
+      </c>
+      <c r="K23" s="160" t="s">
         <v>555</v>
-      </c>
-      <c r="J23" s="162" t="s">
-        <v>556</v>
-      </c>
-      <c r="K23" s="160" t="s">
-        <v>557</v>
       </c>
       <c r="L23" s="160"/>
       <c r="M23" s="160"/>
@@ -28155,27 +28130,27 @@
         <v>2</v>
       </c>
       <c r="B24" s="493" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C24" s="494"/>
       <c r="D24" s="71" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E24" s="69" t="s">
         <v>98</v>
       </c>
       <c r="F24" s="72" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G24" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H24" s="164"/>
       <c r="I24" s="73" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J24" s="165" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="K24" s="166" t="s">
         <v>94</v>
@@ -28189,11 +28164,11 @@
         <v>3</v>
       </c>
       <c r="B25" s="493" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C25" s="494"/>
       <c r="D25" s="70" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E25" s="163" t="s">
         <v>94</v>
@@ -28202,7 +28177,7 @@
         <v>99</v>
       </c>
       <c r="G25" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H25" s="168"/>
       <c r="I25" s="68"/>
@@ -28217,11 +28192,11 @@
         <v>4</v>
       </c>
       <c r="B26" s="493" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C26" s="494"/>
       <c r="D26" s="70" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E26" s="163" t="s">
         <v>94</v>
@@ -28230,7 +28205,7 @@
         <v>99</v>
       </c>
       <c r="G26" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H26" s="168"/>
       <c r="I26" s="68"/>
@@ -28245,11 +28220,11 @@
         <v>5</v>
       </c>
       <c r="B27" s="493" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C27" s="494"/>
       <c r="D27" s="74" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E27" s="163" t="s">
         <v>94</v>
@@ -28258,7 +28233,7 @@
         <v>99</v>
       </c>
       <c r="G27" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H27" s="75"/>
       <c r="I27" s="70"/>
@@ -28277,16 +28252,16 @@
       </c>
       <c r="C28" s="494"/>
       <c r="D28" s="71" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E28" s="69" t="s">
         <v>98</v>
       </c>
       <c r="F28" s="72" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G28" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H28" s="75"/>
       <c r="I28" s="70"/>
@@ -28301,20 +28276,20 @@
         <v>7</v>
       </c>
       <c r="B29" s="493" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C29" s="494"/>
       <c r="D29" s="71" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E29" s="69" t="s">
         <v>98</v>
       </c>
       <c r="F29" s="72" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G29" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H29" s="75"/>
       <c r="I29" s="70"/>
@@ -28329,20 +28304,20 @@
         <v>8</v>
       </c>
       <c r="B30" s="493" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C30" s="494"/>
       <c r="D30" s="71" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E30" s="163" t="s">
         <v>94</v>
       </c>
       <c r="F30" s="72" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G30" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H30" s="75"/>
       <c r="I30" s="70"/>
@@ -28357,20 +28332,20 @@
         <v>9</v>
       </c>
       <c r="B31" s="493" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C31" s="494"/>
       <c r="D31" s="71" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E31" s="69" t="s">
         <v>98</v>
       </c>
       <c r="F31" s="72" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="G31" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H31" s="75"/>
       <c r="I31" s="70"/>
@@ -28385,20 +28360,20 @@
         <v>10</v>
       </c>
       <c r="B32" s="493" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C32" s="494"/>
       <c r="D32" s="71" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E32" s="69" t="s">
         <v>94</v>
       </c>
       <c r="F32" s="72" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G32" s="76" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H32" s="75"/>
       <c r="I32" s="70"/>
@@ -28413,20 +28388,20 @@
         <v>11</v>
       </c>
       <c r="B33" s="493" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C33" s="494"/>
       <c r="D33" s="71" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="E33" s="69" t="s">
         <v>94</v>
       </c>
       <c r="F33" s="72" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="G33" s="76" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H33" s="75"/>
       <c r="I33" s="70"/>
@@ -28441,20 +28416,20 @@
         <v>12</v>
       </c>
       <c r="B34" s="493" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C34" s="494"/>
       <c r="D34" s="71" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E34" s="69" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F34" s="72" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="G34" s="76" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H34" s="75"/>
       <c r="I34" s="70"/>
@@ -28473,15 +28448,15 @@
         <v>305</v>
       </c>
       <c r="B36" s="498" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C36" s="499"/>
       <c r="D36" s="500"/>
       <c r="E36" s="57" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F36" s="511" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="G36" s="512"/>
       <c r="H36" s="513"/>
@@ -28511,7 +28486,7 @@
         <v>92</v>
       </c>
       <c r="B38" s="505" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C38" s="506"/>
       <c r="D38" s="506"/>
@@ -28520,7 +28495,7 @@
       <c r="G38" s="506"/>
       <c r="H38" s="507"/>
       <c r="I38" s="156" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="J38" s="156"/>
       <c r="K38" s="156"/>
@@ -28529,10 +28504,10 @@
     </row>
     <row r="39" spans="1:15" ht="75.75" customHeight="1">
       <c r="A39" s="60" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B39" s="508" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C39" s="502"/>
       <c r="D39" s="502"/>
@@ -28552,7 +28527,7 @@
         <v>301</v>
       </c>
       <c r="B41" s="517" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C41" s="502"/>
       <c r="D41" s="502"/>
@@ -28560,7 +28535,7 @@
       <c r="F41" s="502"/>
       <c r="G41" s="503"/>
       <c r="H41" s="518" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="I41" s="502"/>
       <c r="J41" s="502"/>
@@ -28618,7 +28593,7 @@
         <v>309</v>
       </c>
       <c r="L43" s="64" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="M43" s="63" t="s">
         <v>285</v>
@@ -28629,33 +28604,33 @@
         <v>1</v>
       </c>
       <c r="B44" s="509" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C44" s="510"/>
       <c r="D44" s="159" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E44" s="160" t="s">
         <v>94</v>
       </c>
       <c r="F44" s="161" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G44" s="160" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H44" s="67"/>
       <c r="I44" s="68" t="s">
+        <v>553</v>
+      </c>
+      <c r="J44" s="162" t="s">
+        <v>554</v>
+      </c>
+      <c r="K44" s="160" t="s">
         <v>555</v>
       </c>
-      <c r="J44" s="162" t="s">
-        <v>556</v>
-      </c>
-      <c r="K44" s="160" t="s">
-        <v>557</v>
-      </c>
       <c r="L44" s="170" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="M44" s="160"/>
     </row>
@@ -28671,10 +28646,10 @@
       <c r="G45" s="66"/>
       <c r="H45" s="164"/>
       <c r="I45" s="73" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="J45" s="165" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="K45" s="166" t="s">
         <v>94</v>
@@ -28810,15 +28785,15 @@
         <v>305</v>
       </c>
       <c r="B54" s="498" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C54" s="499"/>
       <c r="D54" s="500"/>
       <c r="E54" s="57" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F54" s="511" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G54" s="524"/>
       <c r="H54" s="525"/>
@@ -28848,7 +28823,7 @@
         <v>92</v>
       </c>
       <c r="B56" s="505" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C56" s="506"/>
       <c r="D56" s="506"/>
@@ -28857,7 +28832,7 @@
       <c r="G56" s="506"/>
       <c r="H56" s="507"/>
       <c r="I56" s="156" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="J56" s="156"/>
       <c r="K56" s="156"/>
@@ -28866,10 +28841,10 @@
     </row>
     <row r="57" spans="1:15" ht="78" customHeight="1">
       <c r="A57" s="60" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B57" s="508" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C57" s="502"/>
       <c r="D57" s="502"/>
@@ -28889,7 +28864,7 @@
         <v>301</v>
       </c>
       <c r="B59" s="517" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C59" s="502"/>
       <c r="D59" s="502"/>
@@ -28897,7 +28872,7 @@
       <c r="F59" s="502"/>
       <c r="G59" s="503"/>
       <c r="H59" s="518" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="I59" s="502"/>
       <c r="J59" s="502"/>
@@ -28955,7 +28930,7 @@
         <v>309</v>
       </c>
       <c r="L61" s="64" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="M61" s="63" t="s">
         <v>285</v>
@@ -28967,30 +28942,30 @@
         <v>1</v>
       </c>
       <c r="B62" s="509" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C62" s="510"/>
       <c r="D62" s="159" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E62" s="160" t="s">
         <v>94</v>
       </c>
       <c r="F62" s="161" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G62" s="160" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H62" s="67"/>
       <c r="I62" s="68" t="s">
+        <v>553</v>
+      </c>
+      <c r="J62" s="162" t="s">
+        <v>554</v>
+      </c>
+      <c r="K62" s="160" t="s">
         <v>555</v>
-      </c>
-      <c r="J62" s="162" t="s">
-        <v>556</v>
-      </c>
-      <c r="K62" s="160" t="s">
-        <v>557</v>
       </c>
       <c r="L62" s="160"/>
       <c r="M62" s="160"/>
@@ -29001,29 +28976,29 @@
         <v>2</v>
       </c>
       <c r="B63" s="495" t="s">
+        <v>556</v>
+      </c>
+      <c r="C63" s="70" t="s">
+        <v>557</v>
+      </c>
+      <c r="D63" s="71" t="s">
         <v>558</v>
-      </c>
-      <c r="C63" s="70" t="s">
-        <v>559</v>
-      </c>
-      <c r="D63" s="71" t="s">
-        <v>560</v>
       </c>
       <c r="E63" s="69" t="s">
         <v>98</v>
       </c>
       <c r="F63" s="72" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G63" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H63" s="164"/>
       <c r="I63" s="73" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J63" s="165" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="K63" s="166" t="s">
         <v>94</v>
@@ -29038,10 +29013,10 @@
       </c>
       <c r="B64" s="496"/>
       <c r="C64" s="70" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D64" s="70" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E64" s="163" t="s">
         <v>94</v>
@@ -29050,7 +29025,7 @@
         <v>99</v>
       </c>
       <c r="G64" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H64" s="168"/>
       <c r="I64" s="68"/>
@@ -29066,10 +29041,10 @@
       </c>
       <c r="B65" s="496"/>
       <c r="C65" s="70" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D65" s="70" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E65" s="163" t="s">
         <v>94</v>
@@ -29078,7 +29053,7 @@
         <v>99</v>
       </c>
       <c r="G65" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H65" s="168"/>
       <c r="I65" s="68"/>
@@ -29094,10 +29069,10 @@
       </c>
       <c r="B66" s="496"/>
       <c r="C66" s="70" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D66" s="74" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E66" s="163" t="s">
         <v>94</v>
@@ -29106,7 +29081,7 @@
         <v>99</v>
       </c>
       <c r="G66" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H66" s="75"/>
       <c r="I66" s="70"/>
@@ -29125,16 +29100,16 @@
         <v>47</v>
       </c>
       <c r="D67" s="71" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E67" s="69" t="s">
         <v>98</v>
       </c>
       <c r="F67" s="72" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G67" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H67" s="75"/>
       <c r="I67" s="70"/>
@@ -29149,19 +29124,19 @@
       </c>
       <c r="B68" s="496"/>
       <c r="C68" s="70" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D68" s="71" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E68" s="69" t="s">
         <v>98</v>
       </c>
       <c r="F68" s="72" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G68" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H68" s="75"/>
       <c r="I68" s="70"/>
@@ -29176,19 +29151,19 @@
       </c>
       <c r="B69" s="496"/>
       <c r="C69" s="70" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D69" s="71" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E69" s="163" t="s">
         <v>94</v>
       </c>
       <c r="F69" s="72" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G69" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H69" s="75"/>
       <c r="I69" s="70"/>
@@ -29203,19 +29178,19 @@
       </c>
       <c r="B70" s="496"/>
       <c r="C70" s="70" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D70" s="71" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E70" s="69" t="s">
         <v>98</v>
       </c>
       <c r="F70" s="72" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="G70" s="163" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H70" s="75"/>
       <c r="I70" s="70"/>
@@ -29230,19 +29205,19 @@
       </c>
       <c r="B71" s="496"/>
       <c r="C71" s="70" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D71" s="71" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E71" s="69" t="s">
         <v>94</v>
       </c>
       <c r="F71" s="72" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G71" s="76" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H71" s="75"/>
       <c r="I71" s="70"/>
@@ -29257,19 +29232,19 @@
       </c>
       <c r="B72" s="496"/>
       <c r="C72" s="172" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D72" s="71" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="E72" s="69" t="s">
         <v>94</v>
       </c>
       <c r="F72" s="72" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="G72" s="76" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H72" s="75"/>
       <c r="I72" s="70"/>
@@ -29284,19 +29259,19 @@
       </c>
       <c r="B73" s="497"/>
       <c r="C73" s="172" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D73" s="71" t="s">
         <v>1016</v>
       </c>
-      <c r="D73" s="71" t="s">
-        <v>1018</v>
-      </c>
       <c r="E73" s="69" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F73" s="72" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="G73" s="76" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H73" s="75"/>
       <c r="I73" s="70"/>
@@ -29350,18 +29325,18 @@
     <row r="79" spans="1:15" ht="15" hidden="1" customHeight="1"/>
     <row r="80" spans="1:15" ht="21.75" hidden="1" customHeight="1">
       <c r="A80" s="56" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B80" s="498" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C80" s="499"/>
       <c r="D80" s="500"/>
       <c r="E80" s="57" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F80" s="530" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G80" s="502"/>
       <c r="H80" s="503"/>
@@ -29391,7 +29366,7 @@
         <v>92</v>
       </c>
       <c r="B82" s="505" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C82" s="506"/>
       <c r="D82" s="506"/>
@@ -29400,7 +29375,7 @@
       <c r="G82" s="506"/>
       <c r="H82" s="507"/>
       <c r="I82" s="156" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="J82" s="156"/>
       <c r="K82" s="156"/>
@@ -29409,10 +29384,10 @@
     </row>
     <row r="83" spans="1:13" ht="18.75" hidden="1" customHeight="1">
       <c r="A83" s="57" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B83" s="526" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C83" s="502"/>
       <c r="D83" s="502"/>
@@ -29432,7 +29407,7 @@
         <v>301</v>
       </c>
       <c r="B85" s="517" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C85" s="502"/>
       <c r="D85" s="502"/>
@@ -29440,7 +29415,7 @@
       <c r="F85" s="502"/>
       <c r="G85" s="503"/>
       <c r="H85" s="518" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="I85" s="502"/>
       <c r="J85" s="502"/>
@@ -29451,7 +29426,7 @@
     <row r="86" spans="1:13" ht="15.75" hidden="1" customHeight="1">
       <c r="A86" s="515"/>
       <c r="B86" s="519" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C86" s="502"/>
       <c r="D86" s="506"/>
@@ -29459,7 +29434,7 @@
       <c r="F86" s="502"/>
       <c r="G86" s="503"/>
       <c r="H86" s="520" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="I86" s="502"/>
       <c r="J86" s="502"/>
@@ -29470,7 +29445,7 @@
     <row r="87" spans="1:13" ht="15.75" hidden="1" customHeight="1">
       <c r="A87" s="516"/>
       <c r="B87" s="521" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C87" s="522"/>
       <c r="D87" s="61" t="s">
@@ -29480,16 +29455,16 @@
         <v>309</v>
       </c>
       <c r="F87" s="63" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G87" s="63" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="H87" s="64" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="J87" s="61" t="s">
         <v>276</v>
@@ -29498,7 +29473,7 @@
         <v>309</v>
       </c>
       <c r="L87" s="64" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="M87" s="63" t="s">
         <v>285</v>
@@ -29509,30 +29484,30 @@
         <v>1</v>
       </c>
       <c r="B88" s="509" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C88" s="510"/>
       <c r="D88" s="159" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E88" s="160" t="s">
         <v>94</v>
       </c>
       <c r="F88" s="161" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G88" s="160" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H88" s="67"/>
       <c r="I88" s="68" t="s">
+        <v>553</v>
+      </c>
+      <c r="J88" s="162" t="s">
+        <v>554</v>
+      </c>
+      <c r="K88" s="160" t="s">
         <v>555</v>
-      </c>
-      <c r="J88" s="162" t="s">
-        <v>556</v>
-      </c>
-      <c r="K88" s="160" t="s">
-        <v>557</v>
       </c>
       <c r="L88" s="161"/>
       <c r="M88" s="160"/>
@@ -29542,25 +29517,25 @@
         <v>2</v>
       </c>
       <c r="B89" s="528" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C89" s="529"/>
       <c r="D89" s="79" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E89" s="66" t="s">
         <v>98</v>
       </c>
       <c r="F89" s="72" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G89" s="66"/>
       <c r="H89" s="164"/>
       <c r="I89" s="73" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="J89" s="165" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="K89" s="166" t="s">
         <v>94</v>
@@ -29573,17 +29548,17 @@
         <v>3</v>
       </c>
       <c r="B90" s="509" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C90" s="510"/>
       <c r="D90" s="80" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E90" s="160" t="s">
         <v>98</v>
       </c>
       <c r="F90" s="72" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G90" s="171"/>
       <c r="H90" s="168"/>
@@ -29739,14 +29714,14 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C10" r:id="rId1" xr:uid="{1CC5EB6F-4631-4D65-833F-3FD7F9AF0ACA}"/>
+    <hyperlink ref="C10" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCBA951-B4E8-4837-8078-FE2FF9090314}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:N110"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -29766,7 +29741,7 @@
         <v>294</v>
       </c>
       <c r="B2" s="380" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C2" s="355"/>
       <c r="D2" s="341"/>
@@ -29774,7 +29749,7 @@
         <v>293</v>
       </c>
       <c r="F2" s="381" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="G2" s="355"/>
       <c r="H2" s="341"/>
@@ -29823,7 +29798,7 @@
         <v>92</v>
       </c>
       <c r="B5" s="415" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C5" s="542"/>
       <c r="D5" s="542"/>
@@ -29932,7 +29907,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C11" s="95"/>
       <c r="D11" s="96"/>
@@ -29940,24 +29915,24 @@
         <v>94</v>
       </c>
       <c r="F11" s="92" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="G11" s="91" t="s">
         <v>95</v>
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J11" s="93"/>
       <c r="K11" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L11" s="92" t="s">
         <v>437</v>
       </c>
       <c r="M11" s="206" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="30">
@@ -29965,12 +29940,12 @@
         <v>2</v>
       </c>
       <c r="B12" s="46" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C12" s="139"/>
       <c r="D12" s="96"/>
       <c r="E12" s="95" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F12" s="92" t="s">
         <v>428</v>
@@ -29980,17 +29955,17 @@
       </c>
       <c r="H12" s="95"/>
       <c r="I12" s="21" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="J12" s="93"/>
       <c r="K12" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L12" s="92" t="s">
         <v>437</v>
       </c>
       <c r="M12" s="207" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -30005,17 +29980,17 @@
       <c r="G13" s="92"/>
       <c r="H13" s="93"/>
       <c r="I13" s="21" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="J13" s="93"/>
       <c r="K13" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L13" s="92" t="s">
         <v>437</v>
       </c>
       <c r="M13" s="207" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="30">
@@ -30030,7 +30005,7 @@
       <c r="G14" s="97"/>
       <c r="H14" s="93"/>
       <c r="I14" s="21" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="J14" s="93"/>
       <c r="K14" s="90" t="s">
@@ -30040,7 +30015,7 @@
         <v>437</v>
       </c>
       <c r="M14" s="208" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="31.5">
@@ -30055,7 +30030,7 @@
       <c r="G15" s="97"/>
       <c r="H15" s="93"/>
       <c r="I15" s="21" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="J15" s="93"/>
       <c r="K15" s="89" t="s">
@@ -30065,7 +30040,7 @@
         <v>437</v>
       </c>
       <c r="M15" s="209" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -30328,7 +30303,7 @@
     <row r="31" spans="1:14" ht="28.5" customHeight="1">
       <c r="A31" s="22"/>
       <c r="B31" s="539" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C31" s="540"/>
       <c r="D31" s="540"/>
@@ -30347,7 +30322,7 @@
         <v>294</v>
       </c>
       <c r="B34" s="380" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C34" s="355"/>
       <c r="D34" s="341"/>
@@ -30355,7 +30330,7 @@
         <v>293</v>
       </c>
       <c r="F34" s="381" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="G34" s="355"/>
       <c r="H34" s="341"/>
@@ -30405,7 +30380,7 @@
         <v>92</v>
       </c>
       <c r="B37" s="359" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C37" s="365"/>
       <c r="D37" s="365"/>
@@ -30525,7 +30500,7 @@
         <v>428</v>
       </c>
       <c r="G43" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H43" s="20"/>
       <c r="I43" s="21"/>
@@ -30539,18 +30514,18 @@
         <v>2</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C44" s="91"/>
       <c r="D44" s="96"/>
       <c r="E44" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F44" s="92" t="s">
         <v>437</v>
       </c>
       <c r="G44" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H44" s="95"/>
       <c r="I44" s="21"/>
@@ -30558,7 +30533,7 @@
       <c r="K44" s="96"/>
       <c r="L44" s="96"/>
       <c r="M44" s="206" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -30566,18 +30541,18 @@
         <v>3</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C45" s="91"/>
       <c r="D45" s="91"/>
       <c r="E45" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F45" s="92" t="s">
         <v>437</v>
       </c>
       <c r="G45" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H45" s="93"/>
       <c r="I45" s="21"/>
@@ -30585,7 +30560,7 @@
       <c r="K45" s="96"/>
       <c r="L45" s="91"/>
       <c r="M45" s="207" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -30593,17 +30568,17 @@
         <v>4</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D46" s="91"/>
       <c r="E46" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F46" s="92" t="s">
         <v>437</v>
       </c>
       <c r="G46" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H46" s="93"/>
       <c r="I46" s="21"/>
@@ -30611,7 +30586,7 @@
       <c r="K46" s="96"/>
       <c r="L46" s="91"/>
       <c r="M46" s="207" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="30">
@@ -30619,18 +30594,18 @@
         <v>5</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C47" s="91"/>
       <c r="D47" s="91"/>
       <c r="E47" s="90" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="F47" s="92" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G47" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H47" s="93"/>
       <c r="I47" s="21"/>
@@ -30638,7 +30613,7 @@
       <c r="K47" s="96"/>
       <c r="L47" s="91"/>
       <c r="M47" s="208" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="31.5">
@@ -30646,7 +30621,7 @@
         <v>6</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C48" s="91"/>
       <c r="D48" s="91"/>
@@ -30663,7 +30638,7 @@
       <c r="K48" s="96"/>
       <c r="L48" s="91"/>
       <c r="M48" s="209" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -30787,7 +30762,7 @@
     <row r="56" spans="1:13" ht="51.75" customHeight="1">
       <c r="A56" s="19"/>
       <c r="B56" s="400" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C56" s="389"/>
       <c r="D56" s="389"/>
@@ -30806,7 +30781,7 @@
         <v>294</v>
       </c>
       <c r="B60" s="380" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C60" s="355"/>
       <c r="D60" s="341"/>
@@ -30814,7 +30789,7 @@
         <v>293</v>
       </c>
       <c r="F60" s="381" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="G60" s="355"/>
       <c r="H60" s="341"/>
@@ -30863,7 +30838,7 @@
         <v>92</v>
       </c>
       <c r="B63" s="359" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C63" s="365"/>
       <c r="D63" s="365"/>
@@ -30983,7 +30958,7 @@
         <v>428</v>
       </c>
       <c r="G69" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H69" s="25"/>
       <c r="I69" s="21"/>
@@ -30997,18 +30972,18 @@
         <v>2</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C70" s="91"/>
       <c r="D70" s="96"/>
       <c r="E70" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F70" s="92" t="s">
         <v>437</v>
       </c>
       <c r="G70" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H70" s="26"/>
       <c r="I70" s="21"/>
@@ -31022,18 +30997,18 @@
         <v>3</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C71" s="91"/>
       <c r="D71" s="91"/>
       <c r="E71" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F71" s="92" t="s">
         <v>437</v>
       </c>
       <c r="G71" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H71" s="95"/>
       <c r="I71" s="21"/>
@@ -31047,17 +31022,17 @@
         <v>4</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D72" s="91"/>
       <c r="E72" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F72" s="92" t="s">
         <v>437</v>
       </c>
       <c r="G72" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H72" s="93"/>
       <c r="I72" s="21"/>
@@ -31071,18 +31046,18 @@
         <v>5</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C73" s="91"/>
       <c r="D73" s="91"/>
       <c r="E73" s="90" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="F73" s="92" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G73" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H73" s="93"/>
       <c r="I73" s="21"/>
@@ -31096,7 +31071,7 @@
         <v>6</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C74" s="91"/>
       <c r="D74" s="91"/>
@@ -31271,7 +31246,7 @@
         <v>16</v>
       </c>
       <c r="B84" s="400" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C84" s="389"/>
       <c r="D84" s="389"/>
@@ -31290,7 +31265,7 @@
         <v>294</v>
       </c>
       <c r="B87" s="380" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C87" s="355"/>
       <c r="D87" s="341"/>
@@ -31298,7 +31273,7 @@
         <v>293</v>
       </c>
       <c r="F87" s="381" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="G87" s="355"/>
       <c r="H87" s="341"/>
@@ -31347,7 +31322,7 @@
         <v>92</v>
       </c>
       <c r="B90" s="359" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C90" s="365"/>
       <c r="D90" s="365"/>
@@ -31456,7 +31431,7 @@
         <v>1</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C96" s="95"/>
       <c r="D96" s="96"/>
@@ -31684,7 +31659,7 @@
     <row r="110" spans="1:13">
       <c r="A110" s="19"/>
       <c r="B110" s="539" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C110" s="540"/>
       <c r="D110" s="540"/>
@@ -31769,7 +31744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD3DA3B-C8B5-4B1E-8CC6-1F01F4DD0EAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:M383"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -31789,7 +31764,7 @@
         <v>294</v>
       </c>
       <c r="B2" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C2" s="405"/>
       <c r="D2" s="406"/>
@@ -31797,7 +31772,7 @@
         <v>293</v>
       </c>
       <c r="F2" s="381" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="G2" s="481"/>
       <c r="H2" s="482"/>
@@ -31846,7 +31821,7 @@
         <v>92</v>
       </c>
       <c r="B5" s="491" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C5" s="567"/>
       <c r="D5" s="567"/>
@@ -31955,12 +31930,12 @@
         <v>1</v>
       </c>
       <c r="B11" s="230" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C11" s="95"/>
       <c r="D11" s="96"/>
       <c r="E11" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F11" s="92" t="s">
         <v>428</v>
@@ -31988,7 +31963,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="230" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C12" s="139"/>
       <c r="D12" s="96"/>
@@ -32021,7 +31996,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C13" s="108"/>
       <c r="D13" s="91"/>
@@ -32127,10 +32102,10 @@
       <c r="F17" s="92"/>
       <c r="G17" s="227"/>
       <c r="H17" s="564" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="J17" s="93"/>
       <c r="K17" s="96" t="s">
@@ -32153,7 +32128,7 @@
       <c r="G18" s="227"/>
       <c r="H18" s="559"/>
       <c r="I18" s="21" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="J18" s="93"/>
       <c r="K18" s="96" t="s">
@@ -32176,7 +32151,7 @@
       <c r="G19" s="227"/>
       <c r="H19" s="559"/>
       <c r="I19" s="21" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="J19" s="93"/>
       <c r="K19" s="96" t="s">
@@ -32199,7 +32174,7 @@
       <c r="G20" s="227"/>
       <c r="H20" s="559"/>
       <c r="I20" s="21" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="J20" s="93"/>
       <c r="K20" s="96" t="s">
@@ -32222,7 +32197,7 @@
       <c r="G21" s="227"/>
       <c r="H21" s="559"/>
       <c r="I21" s="21" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="J21" s="93"/>
       <c r="K21" s="96" t="s">
@@ -32245,7 +32220,7 @@
       <c r="G22" s="227"/>
       <c r="H22" s="559"/>
       <c r="I22" s="21" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="J22" s="93"/>
       <c r="K22" s="96" t="s">
@@ -32268,7 +32243,7 @@
       <c r="G23" s="227"/>
       <c r="H23" s="560"/>
       <c r="I23" s="21" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="J23" s="93"/>
       <c r="K23" s="96" t="s">
@@ -32401,7 +32376,7 @@
     <row r="31" spans="1:13" ht="30.75" customHeight="1">
       <c r="A31" s="232"/>
       <c r="B31" s="565" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C31" s="566"/>
       <c r="D31" s="566"/>
@@ -32420,7 +32395,7 @@
         <v>294</v>
       </c>
       <c r="B35" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C35" s="405"/>
       <c r="D35" s="406"/>
@@ -32428,7 +32403,7 @@
         <v>293</v>
       </c>
       <c r="F35" s="381" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="G35" s="481"/>
       <c r="H35" s="482"/>
@@ -32477,7 +32452,7 @@
         <v>92</v>
       </c>
       <c r="B38" s="491" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C38" s="567"/>
       <c r="D38" s="567"/>
@@ -32586,12 +32561,12 @@
         <v>1</v>
       </c>
       <c r="B44" s="230" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C44" s="95"/>
       <c r="D44" s="96"/>
       <c r="E44" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F44" s="92" t="s">
         <v>428</v>
@@ -32619,12 +32594,12 @@
         <v>2</v>
       </c>
       <c r="B45" s="230" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C45" s="139"/>
       <c r="D45" s="96"/>
       <c r="E45" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F45" s="92" t="s">
         <v>428</v>
@@ -32652,12 +32627,12 @@
         <v>3</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C46" s="108"/>
       <c r="D46" s="91"/>
       <c r="E46" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F46" s="92" t="s">
         <v>428</v>
@@ -32683,12 +32658,12 @@
         <v>4</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C47" s="93"/>
       <c r="D47" s="91"/>
       <c r="E47" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F47" s="92" t="s">
         <v>428</v>
@@ -32764,10 +32739,10 @@
       <c r="F50" s="92"/>
       <c r="G50" s="227"/>
       <c r="H50" s="564" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="I50" s="21" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="J50" s="93"/>
       <c r="K50" s="96" t="s">
@@ -32790,7 +32765,7 @@
       <c r="G51" s="227"/>
       <c r="H51" s="559"/>
       <c r="I51" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J51" s="93"/>
       <c r="K51" s="96" t="s">
@@ -32813,7 +32788,7 @@
       <c r="G52" s="227"/>
       <c r="H52" s="559"/>
       <c r="I52" s="21" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="J52" s="93"/>
       <c r="K52" s="96" t="s">
@@ -32836,7 +32811,7 @@
       <c r="G53" s="227"/>
       <c r="H53" s="560"/>
       <c r="I53" s="21" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="J53" s="93"/>
       <c r="K53" s="96" t="s">
@@ -33020,7 +32995,7 @@
     <row r="64" spans="1:13" ht="31.5" customHeight="1">
       <c r="A64" s="232"/>
       <c r="B64" s="565" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C64" s="566"/>
       <c r="D64" s="566"/>
@@ -33039,7 +33014,7 @@
         <v>294</v>
       </c>
       <c r="B68" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C68" s="405"/>
       <c r="D68" s="406"/>
@@ -33047,7 +33022,7 @@
         <v>293</v>
       </c>
       <c r="F68" s="381" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G68" s="481"/>
       <c r="H68" s="482"/>
@@ -33096,7 +33071,7 @@
         <v>92</v>
       </c>
       <c r="B71" s="491" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C71" s="567"/>
       <c r="D71" s="567"/>
@@ -33205,12 +33180,12 @@
         <v>1</v>
       </c>
       <c r="B77" s="230" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C77" s="95"/>
       <c r="D77" s="96"/>
       <c r="E77" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F77" s="92" t="s">
         <v>428</v>
@@ -33238,7 +33213,7 @@
         <v>2</v>
       </c>
       <c r="B78" s="230" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C78" s="139"/>
       <c r="D78" s="96"/>
@@ -33369,10 +33344,10 @@
       <c r="F83" s="92"/>
       <c r="G83" s="227"/>
       <c r="H83" s="564" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="I83" s="21" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="J83" s="93"/>
       <c r="K83" s="96" t="s">
@@ -33395,7 +33370,7 @@
       <c r="G84" s="227"/>
       <c r="H84" s="559"/>
       <c r="I84" s="21" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="J84" s="93"/>
       <c r="K84" s="96" t="s">
@@ -33418,7 +33393,7 @@
       <c r="G85" s="227"/>
       <c r="H85" s="559"/>
       <c r="I85" s="21" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="J85" s="93"/>
       <c r="K85" s="96" t="s">
@@ -33441,7 +33416,7 @@
       <c r="G86" s="227"/>
       <c r="H86" s="559"/>
       <c r="I86" s="21" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="J86" s="93"/>
       <c r="K86" s="96" t="s">
@@ -33464,7 +33439,7 @@
       <c r="G87" s="227"/>
       <c r="H87" s="560"/>
       <c r="I87" s="21" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="J87" s="93"/>
       <c r="K87" s="96" t="s">
@@ -33631,7 +33606,7 @@
     <row r="97" spans="1:13" ht="33" customHeight="1">
       <c r="A97" s="232"/>
       <c r="B97" s="565" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C97" s="566"/>
       <c r="D97" s="566"/>
@@ -33650,7 +33625,7 @@
         <v>294</v>
       </c>
       <c r="B100" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C100" s="405"/>
       <c r="D100" s="406"/>
@@ -33658,7 +33633,7 @@
         <v>293</v>
       </c>
       <c r="F100" s="381" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="G100" s="481"/>
       <c r="H100" s="482"/>
@@ -33708,7 +33683,7 @@
         <v>92</v>
       </c>
       <c r="B103" s="342" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C103" s="357"/>
       <c r="D103" s="357"/>
@@ -33727,7 +33702,7 @@
         <v>285</v>
       </c>
       <c r="B104" s="384" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C104" s="485"/>
       <c r="D104" s="485"/>
@@ -33830,7 +33805,7 @@
         <v>428</v>
       </c>
       <c r="G109" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H109" s="20"/>
       <c r="I109" s="21" t="s">
@@ -33852,7 +33827,7 @@
         <v>2</v>
       </c>
       <c r="B110" s="247" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C110" s="95"/>
       <c r="D110" s="96"/>
@@ -33885,10 +33860,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="448" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="D111" s="96"/>
       <c r="E111" s="96" t="s">
@@ -33898,7 +33873,7 @@
         <v>99</v>
       </c>
       <c r="G111" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H111" s="93"/>
       <c r="I111" s="21" t="s">
@@ -33919,7 +33894,7 @@
       </c>
       <c r="B112" s="557"/>
       <c r="C112" s="21" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="D112" s="96"/>
       <c r="E112" s="96" t="s">
@@ -33929,7 +33904,7 @@
         <v>99</v>
       </c>
       <c r="G112" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H112" s="93"/>
       <c r="I112" s="21" t="s">
@@ -33950,7 +33925,7 @@
       </c>
       <c r="B113" s="557"/>
       <c r="C113" s="21" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="D113" s="96"/>
       <c r="E113" s="96" t="s">
@@ -33960,7 +33935,7 @@
         <v>99</v>
       </c>
       <c r="G113" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H113" s="93"/>
       <c r="I113" s="21" t="s">
@@ -33981,7 +33956,7 @@
       </c>
       <c r="B114" s="557"/>
       <c r="C114" s="21" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D114" s="96"/>
       <c r="E114" s="96" t="s">
@@ -33991,7 +33966,7 @@
         <v>99</v>
       </c>
       <c r="G114" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H114" s="95"/>
       <c r="I114" s="21" t="s">
@@ -34012,7 +33987,7 @@
       </c>
       <c r="B115" s="557"/>
       <c r="C115" s="21" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D115" s="96"/>
       <c r="E115" s="96" t="s">
@@ -34022,13 +33997,13 @@
         <v>99</v>
       </c>
       <c r="G115" s="242" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H115" s="561" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="I115" s="243" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="J115" s="93"/>
       <c r="K115" s="96" t="s">
@@ -34045,7 +34020,7 @@
       </c>
       <c r="B116" s="557"/>
       <c r="C116" s="21" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D116" s="96"/>
       <c r="E116" s="96" t="s">
@@ -34055,11 +34030,11 @@
         <v>99</v>
       </c>
       <c r="G116" s="242" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H116" s="562"/>
       <c r="I116" s="243" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="J116" s="93"/>
       <c r="K116" s="96" t="s">
@@ -34076,7 +34051,7 @@
       </c>
       <c r="B117" s="419"/>
       <c r="C117" s="21" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D117" s="96"/>
       <c r="E117" s="96" t="s">
@@ -34090,7 +34065,7 @@
       </c>
       <c r="H117" s="562"/>
       <c r="I117" s="243" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="J117" s="93"/>
       <c r="K117" s="96" t="s">
@@ -34113,7 +34088,7 @@
       <c r="G118" s="242"/>
       <c r="H118" s="562"/>
       <c r="I118" s="243" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="J118" s="93"/>
       <c r="K118" s="96" t="s">
@@ -34136,7 +34111,7 @@
       <c r="G119" s="242"/>
       <c r="H119" s="562"/>
       <c r="I119" s="243" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="J119" s="93"/>
       <c r="K119" s="96" t="s">
@@ -34159,7 +34134,7 @@
       <c r="G120" s="242"/>
       <c r="H120" s="562"/>
       <c r="I120" s="243" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="J120" s="93"/>
       <c r="K120" s="96" t="s">
@@ -34180,7 +34155,7 @@
       <c r="G121" s="242"/>
       <c r="H121" s="563"/>
       <c r="I121" s="243" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="J121" s="93"/>
       <c r="K121" s="96" t="s">
@@ -34211,7 +34186,7 @@
     <row r="123" spans="1:13" s="241" customFormat="1" ht="38.25" customHeight="1">
       <c r="A123" s="19"/>
       <c r="B123" s="400" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C123" s="389"/>
       <c r="D123" s="389"/>
@@ -34230,7 +34205,7 @@
         <v>294</v>
       </c>
       <c r="B126" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C126" s="405"/>
       <c r="D126" s="406"/>
@@ -34238,7 +34213,7 @@
         <v>293</v>
       </c>
       <c r="F126" s="381" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="G126" s="481"/>
       <c r="H126" s="482"/>
@@ -34288,7 +34263,7 @@
         <v>92</v>
       </c>
       <c r="B129" s="342" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C129" s="357"/>
       <c r="D129" s="357"/>
@@ -34307,7 +34282,7 @@
         <v>285</v>
       </c>
       <c r="B130" s="384" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C130" s="485"/>
       <c r="D130" s="485"/>
@@ -34410,7 +34385,7 @@
         <v>428</v>
       </c>
       <c r="G135" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H135" s="20"/>
       <c r="I135" s="21" t="s">
@@ -34432,7 +34407,7 @@
         <v>2</v>
       </c>
       <c r="B136" s="247" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C136" s="93"/>
       <c r="D136" s="96"/>
@@ -34465,10 +34440,10 @@
         <v>3</v>
       </c>
       <c r="B137" s="448" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C137" s="21" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D137" s="96"/>
       <c r="E137" s="96" t="s">
@@ -34478,7 +34453,7 @@
         <v>99</v>
       </c>
       <c r="G137" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H137" s="93"/>
       <c r="I137" s="21" t="s">
@@ -34499,7 +34474,7 @@
       </c>
       <c r="B138" s="557"/>
       <c r="C138" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D138" s="96"/>
       <c r="E138" s="96" t="s">
@@ -34509,7 +34484,7 @@
         <v>99</v>
       </c>
       <c r="G138" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H138" s="93"/>
       <c r="I138" s="21" t="s">
@@ -34530,7 +34505,7 @@
       </c>
       <c r="B139" s="557"/>
       <c r="C139" s="21" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D139" s="96"/>
       <c r="E139" s="96" t="s">
@@ -34540,7 +34515,7 @@
         <v>99</v>
       </c>
       <c r="G139" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H139" s="93"/>
       <c r="I139" s="21" t="s">
@@ -34561,7 +34536,7 @@
       </c>
       <c r="B140" s="419"/>
       <c r="C140" s="21" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="D140" s="96"/>
       <c r="E140" s="96" t="s">
@@ -34571,7 +34546,7 @@
         <v>99</v>
       </c>
       <c r="G140" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H140" s="95"/>
       <c r="I140" s="21" t="s">
@@ -34597,10 +34572,10 @@
       <c r="F141" s="92"/>
       <c r="G141" s="242"/>
       <c r="H141" s="561" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="I141" s="243" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="J141" s="93"/>
       <c r="K141" s="96" t="s">
@@ -34623,7 +34598,7 @@
       <c r="G142" s="242"/>
       <c r="H142" s="562"/>
       <c r="I142" s="243" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J142" s="93"/>
       <c r="K142" s="96" t="s">
@@ -34646,7 +34621,7 @@
       <c r="G143" s="242"/>
       <c r="H143" s="562"/>
       <c r="I143" s="243" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="J143" s="93"/>
       <c r="K143" s="96" t="s">
@@ -34669,7 +34644,7 @@
       <c r="G144" s="242"/>
       <c r="H144" s="563"/>
       <c r="I144" s="243" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="J144" s="93"/>
       <c r="K144" s="96" t="s">
@@ -34734,7 +34709,7 @@
     <row r="148" spans="1:13" ht="36" customHeight="1">
       <c r="A148" s="19"/>
       <c r="B148" s="400" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C148" s="389"/>
       <c r="D148" s="389"/>
@@ -34753,7 +34728,7 @@
         <v>294</v>
       </c>
       <c r="B152" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C152" s="405"/>
       <c r="D152" s="406"/>
@@ -34761,7 +34736,7 @@
         <v>293</v>
       </c>
       <c r="F152" s="381" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="G152" s="481"/>
       <c r="H152" s="482"/>
@@ -34811,7 +34786,7 @@
         <v>92</v>
       </c>
       <c r="B155" s="342" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C155" s="357"/>
       <c r="D155" s="357"/>
@@ -34830,7 +34805,7 @@
         <v>285</v>
       </c>
       <c r="B156" s="384" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C156" s="485"/>
       <c r="D156" s="485"/>
@@ -34933,7 +34908,7 @@
         <v>428</v>
       </c>
       <c r="G161" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H161" s="20"/>
       <c r="I161" s="21" t="s">
@@ -34955,7 +34930,7 @@
         <v>2</v>
       </c>
       <c r="B162" s="247" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C162" s="93"/>
       <c r="D162" s="96"/>
@@ -34988,10 +34963,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="448" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="D163" s="96"/>
       <c r="E163" s="96" t="s">
@@ -35001,7 +34976,7 @@
         <v>99</v>
       </c>
       <c r="G163" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H163" s="93"/>
       <c r="I163" s="21" t="s">
@@ -35022,7 +34997,7 @@
       </c>
       <c r="B164" s="557"/>
       <c r="C164" s="21" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="D164" s="96"/>
       <c r="E164" s="96" t="s">
@@ -35032,7 +35007,7 @@
         <v>99</v>
       </c>
       <c r="G164" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H164" s="93"/>
       <c r="I164" s="21" t="s">
@@ -35053,7 +35028,7 @@
       </c>
       <c r="B165" s="557"/>
       <c r="C165" s="21" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D165" s="96"/>
       <c r="E165" s="96" t="s">
@@ -35063,7 +35038,7 @@
         <v>99</v>
       </c>
       <c r="G165" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H165" s="93"/>
       <c r="I165" s="21" t="s">
@@ -35084,7 +35059,7 @@
       </c>
       <c r="B166" s="557"/>
       <c r="C166" s="21" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D166" s="96"/>
       <c r="E166" s="96" t="s">
@@ -35094,7 +35069,7 @@
         <v>99</v>
       </c>
       <c r="G166" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H166" s="95"/>
       <c r="I166" s="21" t="s">
@@ -35115,7 +35090,7 @@
       </c>
       <c r="B167" s="419"/>
       <c r="C167" s="21" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D167" s="96"/>
       <c r="E167" s="96" t="s">
@@ -35125,13 +35100,13 @@
         <v>99</v>
       </c>
       <c r="G167" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H167" s="558" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="I167" s="21" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="J167" s="93"/>
       <c r="K167" s="96" t="s">
@@ -35154,7 +35129,7 @@
       <c r="G168" s="91"/>
       <c r="H168" s="559"/>
       <c r="I168" s="21" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="J168" s="93"/>
       <c r="K168" s="96" t="s">
@@ -35177,7 +35152,7 @@
       <c r="G169" s="91"/>
       <c r="H169" s="559"/>
       <c r="I169" s="21" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="J169" s="93"/>
       <c r="K169" s="96" t="s">
@@ -35200,7 +35175,7 @@
       <c r="G170" s="91"/>
       <c r="H170" s="559"/>
       <c r="I170" s="21" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="J170" s="93"/>
       <c r="K170" s="96" t="s">
@@ -35223,7 +35198,7 @@
       <c r="G171" s="91"/>
       <c r="H171" s="560"/>
       <c r="I171" s="21" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="J171" s="93"/>
       <c r="K171" s="96" t="s">
@@ -35271,7 +35246,7 @@
     <row r="174" spans="1:13" ht="32.25" customHeight="1">
       <c r="A174" s="19"/>
       <c r="B174" s="400" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C174" s="389"/>
       <c r="D174" s="389"/>
@@ -35290,7 +35265,7 @@
         <v>294</v>
       </c>
       <c r="B178" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C178" s="405"/>
       <c r="D178" s="406"/>
@@ -35298,7 +35273,7 @@
         <v>293</v>
       </c>
       <c r="F178" s="381" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="G178" s="481"/>
       <c r="H178" s="482"/>
@@ -35348,7 +35323,7 @@
         <v>92</v>
       </c>
       <c r="B181" s="342" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C181" s="357"/>
       <c r="D181" s="357"/>
@@ -35468,10 +35443,10 @@
         <v>428</v>
       </c>
       <c r="G187" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H187" s="20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I187" s="21"/>
       <c r="J187" s="93"/>
@@ -35484,7 +35459,7 @@
         <v>2</v>
       </c>
       <c r="B188" s="21" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C188" s="93"/>
       <c r="D188" s="96"/>
@@ -35495,7 +35470,7 @@
         <v>99</v>
       </c>
       <c r="G188" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H188" s="95"/>
       <c r="I188" s="21"/>
@@ -35509,7 +35484,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="21" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C189" s="93"/>
       <c r="D189" s="96"/>
@@ -35520,7 +35495,7 @@
         <v>99</v>
       </c>
       <c r="G189" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H189" s="93"/>
       <c r="I189" s="21"/>
@@ -35534,7 +35509,7 @@
         <v>4</v>
       </c>
       <c r="B190" s="21" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C190" s="93"/>
       <c r="D190" s="96"/>
@@ -35545,7 +35520,7 @@
         <v>99</v>
       </c>
       <c r="G190" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H190" s="93"/>
       <c r="I190" s="21"/>
@@ -35559,7 +35534,7 @@
         <v>5</v>
       </c>
       <c r="B191" s="21" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C191" s="93"/>
       <c r="D191" s="96"/>
@@ -35570,7 +35545,7 @@
         <v>99</v>
       </c>
       <c r="G191" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H191" s="93"/>
       <c r="I191" s="21"/>
@@ -35584,7 +35559,7 @@
         <v>6</v>
       </c>
       <c r="B192" s="21" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C192" s="93"/>
       <c r="D192" s="96"/>
@@ -35595,7 +35570,7 @@
         <v>99</v>
       </c>
       <c r="G192" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H192" s="93"/>
       <c r="I192" s="21"/>
@@ -35609,7 +35584,7 @@
         <v>7</v>
       </c>
       <c r="B193" s="21" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C193" s="93"/>
       <c r="D193" s="96"/>
@@ -35620,7 +35595,7 @@
         <v>99</v>
       </c>
       <c r="G193" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H193" s="19"/>
       <c r="I193" s="21"/>
@@ -35634,7 +35609,7 @@
         <v>8</v>
       </c>
       <c r="B194" s="21" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C194" s="93"/>
       <c r="D194" s="96"/>
@@ -35742,7 +35717,7 @@
     <row r="200" spans="1:13" ht="39" customHeight="1">
       <c r="A200" s="19"/>
       <c r="B200" s="400" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C200" s="389"/>
       <c r="D200" s="389"/>
@@ -35761,7 +35736,7 @@
         <v>294</v>
       </c>
       <c r="B204" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C204" s="405"/>
       <c r="D204" s="406"/>
@@ -35769,7 +35744,7 @@
         <v>293</v>
       </c>
       <c r="F204" s="381" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G204" s="481"/>
       <c r="H204" s="482"/>
@@ -35819,7 +35794,7 @@
         <v>92</v>
       </c>
       <c r="B207" s="342" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C207" s="357"/>
       <c r="D207" s="357"/>
@@ -35939,10 +35914,10 @@
         <v>428</v>
       </c>
       <c r="G213" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H213" s="20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I213" s="21"/>
       <c r="J213" s="93"/>
@@ -35955,7 +35930,7 @@
         <v>2</v>
       </c>
       <c r="B214" s="21" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C214" s="93"/>
       <c r="D214" s="96"/>
@@ -35966,7 +35941,7 @@
         <v>99</v>
       </c>
       <c r="G214" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H214" s="95"/>
       <c r="I214" s="21"/>
@@ -35980,7 +35955,7 @@
         <v>3</v>
       </c>
       <c r="B215" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C215" s="93"/>
       <c r="D215" s="96"/>
@@ -35991,7 +35966,7 @@
         <v>99</v>
       </c>
       <c r="G215" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H215" s="93"/>
       <c r="I215" s="21"/>
@@ -36005,7 +35980,7 @@
         <v>4</v>
       </c>
       <c r="B216" s="21" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C216" s="93"/>
       <c r="D216" s="96"/>
@@ -36016,7 +35991,7 @@
         <v>99</v>
       </c>
       <c r="G216" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H216" s="93"/>
       <c r="I216" s="21"/>
@@ -36030,7 +36005,7 @@
         <v>5</v>
       </c>
       <c r="B217" s="21" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C217" s="93"/>
       <c r="D217" s="96"/>
@@ -36041,7 +36016,7 @@
         <v>99</v>
       </c>
       <c r="G217" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H217" s="93"/>
       <c r="I217" s="21"/>
@@ -36189,7 +36164,7 @@
     <row r="226" spans="1:13" ht="39" customHeight="1">
       <c r="A226" s="19"/>
       <c r="B226" s="400" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C226" s="389"/>
       <c r="D226" s="389"/>
@@ -36208,7 +36183,7 @@
         <v>294</v>
       </c>
       <c r="B230" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C230" s="405"/>
       <c r="D230" s="406"/>
@@ -36216,7 +36191,7 @@
         <v>293</v>
       </c>
       <c r="F230" s="381" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="G230" s="481"/>
       <c r="H230" s="482"/>
@@ -36266,7 +36241,7 @@
         <v>92</v>
       </c>
       <c r="B233" s="342" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C233" s="357"/>
       <c r="D233" s="357"/>
@@ -36386,10 +36361,10 @@
         <v>428</v>
       </c>
       <c r="G239" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H239" s="20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I239" s="21"/>
       <c r="J239" s="93"/>
@@ -36402,7 +36377,7 @@
         <v>2</v>
       </c>
       <c r="B240" s="21" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C240" s="93"/>
       <c r="D240" s="96"/>
@@ -36413,7 +36388,7 @@
         <v>99</v>
       </c>
       <c r="G240" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H240" s="95"/>
       <c r="I240" s="21"/>
@@ -36427,7 +36402,7 @@
         <v>3</v>
       </c>
       <c r="B241" s="21" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C241" s="93"/>
       <c r="D241" s="96"/>
@@ -36438,7 +36413,7 @@
         <v>99</v>
       </c>
       <c r="G241" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H241" s="93"/>
       <c r="I241" s="21"/>
@@ -36452,7 +36427,7 @@
         <v>4</v>
       </c>
       <c r="B242" s="21" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C242" s="93"/>
       <c r="D242" s="96"/>
@@ -36463,7 +36438,7 @@
         <v>99</v>
       </c>
       <c r="G242" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H242" s="93"/>
       <c r="I242" s="21"/>
@@ -36477,7 +36452,7 @@
         <v>5</v>
       </c>
       <c r="B243" s="21" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C243" s="93"/>
       <c r="D243" s="96"/>
@@ -36488,7 +36463,7 @@
         <v>99</v>
       </c>
       <c r="G243" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H243" s="93"/>
       <c r="I243" s="21"/>
@@ -36502,7 +36477,7 @@
         <v>6</v>
       </c>
       <c r="B244" s="21" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C244" s="93"/>
       <c r="D244" s="96"/>
@@ -36513,7 +36488,7 @@
         <v>99</v>
       </c>
       <c r="G244" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H244" s="93"/>
       <c r="I244" s="21"/>
@@ -36644,7 +36619,7 @@
     <row r="252" spans="1:13" ht="31.5" customHeight="1">
       <c r="A252" s="19"/>
       <c r="B252" s="400" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C252" s="389"/>
       <c r="D252" s="389"/>
@@ -36663,7 +36638,7 @@
         <v>294</v>
       </c>
       <c r="B256" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C256" s="405"/>
       <c r="D256" s="406"/>
@@ -36671,7 +36646,7 @@
         <v>293</v>
       </c>
       <c r="F256" s="381" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G256" s="355"/>
       <c r="H256" s="341"/>
@@ -36720,7 +36695,7 @@
         <v>92</v>
       </c>
       <c r="B259" s="342" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C259" s="357"/>
       <c r="D259" s="357"/>
@@ -36829,7 +36804,7 @@
         <v>1</v>
       </c>
       <c r="B265" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C265" s="95"/>
       <c r="D265" s="96"/>
@@ -36843,7 +36818,7 @@
         <v>95</v>
       </c>
       <c r="H265" s="20" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="I265" s="21"/>
       <c r="J265" s="93"/>
@@ -36856,7 +36831,7 @@
         <v>2</v>
       </c>
       <c r="B266" s="21" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C266" s="93"/>
       <c r="D266" s="96"/>
@@ -36867,7 +36842,7 @@
         <v>99</v>
       </c>
       <c r="G266" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H266" s="26"/>
       <c r="I266" s="21"/>
@@ -36881,7 +36856,7 @@
         <v>3</v>
       </c>
       <c r="B267" s="21" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C267" s="93"/>
       <c r="D267" s="96"/>
@@ -37077,7 +37052,7 @@
     <row r="279" spans="1:13" ht="33.75" customHeight="1">
       <c r="A279" s="19"/>
       <c r="B279" s="554" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C279" s="555"/>
       <c r="D279" s="555"/>
@@ -37096,7 +37071,7 @@
         <v>294</v>
       </c>
       <c r="B283" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C283" s="405"/>
       <c r="D283" s="406"/>
@@ -37104,7 +37079,7 @@
         <v>293</v>
       </c>
       <c r="F283" s="381" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G283" s="355"/>
       <c r="H283" s="341"/>
@@ -37153,7 +37128,7 @@
         <v>92</v>
       </c>
       <c r="B286" s="342" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C286" s="357"/>
       <c r="D286" s="357"/>
@@ -37273,10 +37248,10 @@
         <v>428</v>
       </c>
       <c r="G292" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H292" s="20" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="I292" s="21"/>
       <c r="J292" s="93"/>
@@ -37289,7 +37264,7 @@
         <v>2</v>
       </c>
       <c r="B293" s="21" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C293" s="93"/>
       <c r="D293" s="96"/>
@@ -37297,10 +37272,10 @@
         <v>94</v>
       </c>
       <c r="F293" s="92" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G293" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H293" s="26"/>
       <c r="I293" s="21"/>
@@ -37314,7 +37289,7 @@
         <v>3</v>
       </c>
       <c r="B294" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C294" s="93"/>
       <c r="D294" s="96"/>
@@ -37322,10 +37297,10 @@
         <v>94</v>
       </c>
       <c r="F294" s="92" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G294" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H294" s="95"/>
       <c r="I294" s="21"/>
@@ -37339,7 +37314,7 @@
         <v>4</v>
       </c>
       <c r="B295" s="21" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C295" s="93"/>
       <c r="D295" s="96"/>
@@ -37347,7 +37322,7 @@
         <v>94</v>
       </c>
       <c r="F295" s="92" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G295" s="91"/>
       <c r="H295" s="93"/>
@@ -37512,7 +37487,7 @@
     <row r="306" spans="1:13" ht="33" customHeight="1">
       <c r="A306" s="19"/>
       <c r="B306" s="400" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C306" s="389"/>
       <c r="D306" s="389"/>
@@ -37531,7 +37506,7 @@
         <v>294</v>
       </c>
       <c r="B310" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C310" s="405"/>
       <c r="D310" s="406"/>
@@ -37539,7 +37514,7 @@
         <v>293</v>
       </c>
       <c r="F310" s="381" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="G310" s="355"/>
       <c r="H310" s="341"/>
@@ -37588,7 +37563,7 @@
         <v>92</v>
       </c>
       <c r="B313" s="342" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C313" s="357"/>
       <c r="D313" s="357"/>
@@ -37708,10 +37683,10 @@
         <v>428</v>
       </c>
       <c r="G319" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H319" s="20" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="I319" s="21"/>
       <c r="J319" s="93"/>
@@ -37724,7 +37699,7 @@
         <v>2</v>
       </c>
       <c r="B320" s="21" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C320" s="93"/>
       <c r="D320" s="96"/>
@@ -37735,7 +37710,7 @@
         <v>99</v>
       </c>
       <c r="G320" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H320" s="26"/>
       <c r="I320" s="21"/>
@@ -37935,7 +37910,7 @@
     <row r="333" spans="1:13" ht="32.25" customHeight="1">
       <c r="A333" s="19"/>
       <c r="B333" s="400" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C333" s="389"/>
       <c r="D333" s="389"/>
@@ -37954,7 +37929,7 @@
         <v>294</v>
       </c>
       <c r="B336" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C336" s="405"/>
       <c r="D336" s="406"/>
@@ -37962,7 +37937,7 @@
         <v>293</v>
       </c>
       <c r="F336" s="381" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G336" s="481"/>
       <c r="H336" s="482"/>
@@ -38012,7 +37987,7 @@
         <v>92</v>
       </c>
       <c r="B339" s="342" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C339" s="357"/>
       <c r="D339" s="357"/>
@@ -38133,10 +38108,10 @@
         <v>428</v>
       </c>
       <c r="G345" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H345" s="20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I345" s="21"/>
       <c r="J345" s="93"/>
@@ -38149,7 +38124,7 @@
         <v>2</v>
       </c>
       <c r="B346" s="259" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C346" s="93"/>
       <c r="D346" s="96"/>
@@ -38359,7 +38334,7 @@
     <row r="358" spans="1:13" s="253" customFormat="1" ht="33" customHeight="1">
       <c r="A358" s="19"/>
       <c r="B358" s="400" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C358" s="389"/>
       <c r="D358" s="389"/>
@@ -38378,7 +38353,7 @@
         <v>294</v>
       </c>
       <c r="B360" s="380" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C360" s="405"/>
       <c r="D360" s="406"/>
@@ -38386,7 +38361,7 @@
         <v>293</v>
       </c>
       <c r="F360" s="381" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="G360" s="355"/>
       <c r="H360" s="341"/>
@@ -38435,7 +38410,7 @@
         <v>92</v>
       </c>
       <c r="B363" s="342" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C363" s="357"/>
       <c r="D363" s="357"/>
@@ -38556,10 +38531,10 @@
         <v>428</v>
       </c>
       <c r="G369" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H369" s="20" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="I369" s="21"/>
       <c r="J369" s="93"/>
@@ -38767,7 +38742,7 @@
     <row r="383" spans="1:13" s="272" customFormat="1" ht="41.25" customHeight="1">
       <c r="A383" s="19"/>
       <c r="B383" s="400" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C383" s="389"/>
       <c r="D383" s="389"/>
@@ -39010,7 +38985,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:D52"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -39425,7 +39400,7 @@
         <v>1100</v>
       </c>
       <c r="C45" s="93" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D45" s="114"/>
     </row>
@@ -39434,7 +39409,7 @@
         <v>1101</v>
       </c>
       <c r="C46" s="93" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D46" s="114"/>
     </row>
@@ -39443,7 +39418,7 @@
         <v>1102</v>
       </c>
       <c r="C47" s="93" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D47" s="114"/>
     </row>
@@ -39457,7 +39432,7 @@
         <v>1200</v>
       </c>
       <c r="C49" s="93" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D49" s="114"/>
     </row>
@@ -39471,7 +39446,7 @@
         <v>1301</v>
       </c>
       <c r="C51" s="93" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D51" s="114"/>
     </row>
@@ -39490,7 +39465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:M72"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -39585,7 +39560,7 @@
         <v>302</v>
       </c>
       <c r="B6" s="368" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C6" s="355"/>
       <c r="D6" s="355"/>
@@ -39754,7 +39729,7 @@
       <c r="F15" s="298"/>
       <c r="G15" s="297"/>
       <c r="H15" s="356" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="I15" s="356"/>
       <c r="J15" s="356"/>
@@ -39776,7 +39751,7 @@
         <v>293</v>
       </c>
       <c r="F17" s="381" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="G17" s="355"/>
       <c r="H17" s="341"/>
@@ -39795,7 +39770,7 @@
         <v>292</v>
       </c>
       <c r="F18" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G18" s="365"/>
       <c r="H18" s="366"/>
@@ -39844,7 +39819,7 @@
         <v>285</v>
       </c>
       <c r="B21" s="368" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C21" s="355"/>
       <c r="D21" s="355"/>
@@ -39937,7 +39912,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="54" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C26" s="49"/>
       <c r="D26" s="96"/>
@@ -39968,7 +39943,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="220" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C27" s="294"/>
       <c r="D27" s="21"/>
@@ -40008,7 +39983,7 @@
     <row r="29" spans="1:13" s="291" customFormat="1" ht="31.5" customHeight="1">
       <c r="A29" s="296"/>
       <c r="B29" s="356" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C29" s="356"/>
       <c r="D29" s="356"/>
@@ -40029,7 +40004,7 @@
         <v>294</v>
       </c>
       <c r="B31" s="380" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C31" s="355"/>
       <c r="D31" s="341"/>
@@ -40037,7 +40012,7 @@
         <v>293</v>
       </c>
       <c r="F31" s="381" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="G31" s="355"/>
       <c r="H31" s="341"/>
@@ -40056,7 +40031,7 @@
         <v>292</v>
       </c>
       <c r="F32" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G32" s="365"/>
       <c r="H32" s="366"/>
@@ -40067,7 +40042,7 @@
         <v>90</v>
       </c>
       <c r="B33" s="367" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C33" s="355"/>
       <c r="D33" s="355"/>
@@ -40086,7 +40061,7 @@
         <v>92</v>
       </c>
       <c r="B34" s="359" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C34" s="365"/>
       <c r="D34" s="365"/>
@@ -40196,12 +40171,12 @@
         <v>1</v>
       </c>
       <c r="B40" s="89" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C40" s="90"/>
       <c r="D40" s="90"/>
       <c r="E40" s="90" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F40" s="92" t="s">
         <v>437</v>
@@ -40221,12 +40196,12 @@
         <v>2</v>
       </c>
       <c r="B41" s="93" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C41" s="294"/>
       <c r="D41" s="21"/>
       <c r="E41" s="21" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F41" s="92" t="s">
         <v>437</v>
@@ -40246,12 +40221,12 @@
         <v>3</v>
       </c>
       <c r="B42" s="93" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C42" s="294"/>
       <c r="D42" s="21"/>
       <c r="E42" s="90" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F42" s="92" t="s">
         <v>437</v>
@@ -40269,7 +40244,7 @@
     <row r="43" spans="1:13" s="291" customFormat="1" ht="29.25" customHeight="1">
       <c r="A43" s="19"/>
       <c r="B43" s="356" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C43" s="356"/>
       <c r="D43" s="356"/>
@@ -40852,7 +40827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:M105"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -41416,7 +41391,7 @@
     <row r="30" spans="1:13" ht="51" customHeight="1">
       <c r="A30" s="19"/>
       <c r="B30" s="388" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C30" s="389"/>
       <c r="D30" s="389"/>
@@ -41681,7 +41656,7 @@
     <row r="45" spans="1:13">
       <c r="A45" s="19"/>
       <c r="B45" s="21" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
@@ -41779,7 +41754,7 @@
         <v>302</v>
       </c>
       <c r="B52" s="368" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C52" s="355"/>
       <c r="D52" s="355"/>
@@ -41910,7 +41885,7 @@
         <v>314</v>
       </c>
       <c r="F58" s="92" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G58" s="397" t="s">
         <v>318</v>
@@ -42002,7 +41977,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C62" s="93"/>
       <c r="D62" s="91"/>
@@ -42027,7 +42002,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="29" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C63" s="30"/>
       <c r="D63" s="27"/>
@@ -42050,7 +42025,7 @@
     <row r="64" spans="1:13" ht="60" customHeight="1">
       <c r="A64" s="19"/>
       <c r="B64" s="400" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C64" s="355"/>
       <c r="D64" s="355"/>
@@ -42278,7 +42253,7 @@
         <v>94</v>
       </c>
       <c r="F76" s="92" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G76" s="91" t="s">
         <v>95</v>
@@ -42354,7 +42329,7 @@
         <v>294</v>
       </c>
       <c r="B82" s="380" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C82" s="355"/>
       <c r="D82" s="341"/>
@@ -42362,7 +42337,7 @@
         <v>293</v>
       </c>
       <c r="F82" s="396" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G82" s="355"/>
       <c r="H82" s="341"/>
@@ -42412,7 +42387,7 @@
         <v>92</v>
       </c>
       <c r="B85" s="359" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C85" s="365"/>
       <c r="D85" s="365"/>
@@ -42431,7 +42406,7 @@
         <v>285</v>
       </c>
       <c r="B86" s="368" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C86" s="355"/>
       <c r="D86" s="355"/>
@@ -42523,7 +42498,7 @@
         <v>1</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C91" s="95"/>
       <c r="D91" s="96"/>
@@ -42531,7 +42506,7 @@
         <v>94</v>
       </c>
       <c r="F91" s="92" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G91" s="91" t="s">
         <v>95</v>
@@ -42562,7 +42537,7 @@
         <v>94</v>
       </c>
       <c r="F92" s="92" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G92" s="96" t="s">
         <v>95</v>
@@ -42685,7 +42660,7 @@
         <v>7</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C97" s="114"/>
       <c r="D97" s="116"/>
@@ -42710,7 +42685,7 @@
         <v>8</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C98" s="114"/>
       <c r="D98" s="116"/>
@@ -42735,7 +42710,7 @@
         <v>9</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C99" s="114"/>
       <c r="D99" s="116"/>
@@ -42760,7 +42735,7 @@
         <v>10</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C100" s="114"/>
       <c r="D100" s="116"/>
@@ -42785,7 +42760,7 @@
         <v>11</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C101" s="114"/>
       <c r="D101" s="116"/>
@@ -42810,7 +42785,7 @@
         <v>12</v>
       </c>
       <c r="B102" s="53" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C102" s="114"/>
       <c r="D102" s="116"/>
@@ -42835,7 +42810,7 @@
         <v>13</v>
       </c>
       <c r="B103" s="53" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C103" s="114"/>
       <c r="D103" s="116"/>
@@ -42860,7 +42835,7 @@
         <v>14</v>
       </c>
       <c r="B104" s="53" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C104" s="114"/>
       <c r="D104" s="116"/>
@@ -42883,7 +42858,7 @@
     <row r="105" spans="1:13" ht="78.75" customHeight="1">
       <c r="A105" s="114"/>
       <c r="B105" s="412" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C105" s="413"/>
       <c r="D105" s="413"/>
@@ -42892,7 +42867,7 @@
       <c r="G105" s="414"/>
       <c r="H105" s="114"/>
       <c r="I105" s="385" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="J105" s="386"/>
       <c r="K105" s="386"/>
@@ -43000,7 +42975,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:N187"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -43075,7 +43050,7 @@
         <v>92</v>
       </c>
       <c r="B5" s="356" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C5" s="433"/>
       <c r="D5" s="433"/>
@@ -43094,7 +43069,7 @@
         <v>302</v>
       </c>
       <c r="B6" s="368" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C6" s="355"/>
       <c r="D6" s="355"/>
@@ -44856,17 +44831,17 @@
       <c r="G88" s="315"/>
       <c r="H88" s="338"/>
       <c r="I88" s="21" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="J88" s="93"/>
       <c r="K88" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L88" s="96" t="s">
         <v>437</v>
       </c>
       <c r="M88" s="429" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="89" spans="1:13" s="313" customFormat="1">
@@ -44879,11 +44854,11 @@
       <c r="G89" s="315"/>
       <c r="H89" s="338"/>
       <c r="I89" s="21" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="J89" s="93"/>
       <c r="K89" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L89" s="96" t="s">
         <v>437</v>
@@ -44900,11 +44875,11 @@
       <c r="G90" s="315"/>
       <c r="H90" s="338"/>
       <c r="I90" s="21" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="J90" s="93"/>
       <c r="K90" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L90" s="96" t="s">
         <v>437</v>
@@ -44921,7 +44896,7 @@
       <c r="G91" s="326"/>
       <c r="H91" s="338"/>
       <c r="I91" s="21" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="J91" s="93"/>
       <c r="K91" s="96" t="s">
@@ -44931,7 +44906,7 @@
         <v>437</v>
       </c>
       <c r="M91" s="434" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="92" spans="1:13" s="324" customFormat="1">
@@ -44944,7 +44919,7 @@
       <c r="G92" s="326"/>
       <c r="H92" s="338"/>
       <c r="I92" s="21" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="J92" s="93"/>
       <c r="K92" s="96" t="s">
@@ -44965,7 +44940,7 @@
       <c r="G93" s="326"/>
       <c r="H93" s="338"/>
       <c r="I93" s="21" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="J93" s="93"/>
       <c r="K93" s="96" t="s">
@@ -44986,7 +44961,7 @@
       <c r="G94" s="326"/>
       <c r="H94" s="338"/>
       <c r="I94" s="21" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="J94" s="93"/>
       <c r="K94" s="96" t="s">
@@ -45007,17 +44982,17 @@
       <c r="G95" s="97"/>
       <c r="H95" s="339"/>
       <c r="I95" s="21" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="J95" s="93"/>
       <c r="K95" s="96" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L95" s="96" t="s">
         <v>99</v>
       </c>
       <c r="M95" s="136" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -45146,7 +45121,7 @@
         <v>302</v>
       </c>
       <c r="B103" s="411" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C103" s="355"/>
       <c r="D103" s="355"/>
@@ -45379,7 +45354,7 @@
         <v>92</v>
       </c>
       <c r="B117" s="415" t="s">
-        <v>443</v>
+        <v>1051</v>
       </c>
       <c r="C117" s="365"/>
       <c r="D117" s="365"/>
@@ -45529,7 +45504,7 @@
         <v>94</v>
       </c>
       <c r="F124" s="92" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G124" s="91" t="s">
         <v>95</v>
@@ -45674,7 +45649,7 @@
     <row r="129" spans="1:13" ht="126" customHeight="1">
       <c r="A129" s="19"/>
       <c r="B129" s="400" t="s">
-        <v>444</v>
+        <v>1050</v>
       </c>
       <c r="C129" s="386"/>
       <c r="D129" s="386"/>
@@ -45889,7 +45864,7 @@
         <v>214</v>
       </c>
       <c r="M141" s="92" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="30">
@@ -45905,7 +45880,7 @@
         <v>94</v>
       </c>
       <c r="F142" s="138" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G142" s="91" t="s">
         <v>95</v>
@@ -46033,7 +46008,7 @@
         <v>92</v>
       </c>
       <c r="B151" s="359" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C151" s="365"/>
       <c r="D151" s="365"/>
@@ -46175,7 +46150,7 @@
         <v>94</v>
       </c>
       <c r="F158" s="138" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G158" s="91" t="s">
         <v>95</v>
@@ -46257,7 +46232,7 @@
     <row r="162" spans="1:13" ht="51.75" customHeight="1">
       <c r="A162" s="19"/>
       <c r="B162" s="400" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C162" s="389"/>
       <c r="D162" s="389"/>
@@ -46276,7 +46251,7 @@
         <v>294</v>
       </c>
       <c r="B164" s="380" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C164" s="355"/>
       <c r="D164" s="341"/>
@@ -46284,7 +46259,7 @@
         <v>293</v>
       </c>
       <c r="F164" s="381" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="G164" s="355"/>
       <c r="H164" s="341"/>
@@ -46304,7 +46279,7 @@
         <v>292</v>
       </c>
       <c r="F165" s="364" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G165" s="365"/>
       <c r="H165" s="366"/>
@@ -46315,7 +46290,7 @@
         <v>90</v>
       </c>
       <c r="B166" s="379" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C166" s="355"/>
       <c r="D166" s="355"/>
@@ -46334,7 +46309,7 @@
         <v>92</v>
       </c>
       <c r="B167" s="359" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C167" s="365"/>
       <c r="D167" s="365"/>
@@ -46477,7 +46452,7 @@
         <v>94</v>
       </c>
       <c r="F174" s="138" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G174" s="91" t="s">
         <v>95</v>
@@ -46522,7 +46497,7 @@
     <row r="177" spans="1:13" s="226" customFormat="1" ht="39" customHeight="1">
       <c r="A177" s="19"/>
       <c r="B177" s="400" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C177" s="389"/>
       <c r="D177" s="389"/>
@@ -46638,12 +46613,12 @@
     </row>
     <row r="186" spans="1:13" ht="29.25" customHeight="1">
       <c r="B186" s="426" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C186" s="427"/>
       <c r="D186" s="425"/>
       <c r="E186" s="424" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="F186" s="425"/>
       <c r="G186" s="421" t="s">
@@ -46654,16 +46629,16 @@
     </row>
     <row r="187" spans="1:13" s="299" customFormat="1" ht="32.25" customHeight="1">
       <c r="B187" s="437" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C187" s="438"/>
       <c r="D187" s="439"/>
       <c r="E187" s="424" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="F187" s="425"/>
       <c r="G187" s="421" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="H187" s="422"/>
       <c r="I187" s="423"/>
@@ -46797,7 +46772,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:N190"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -47162,7 +47137,7 @@
         <v>107</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="J17" s="93"/>
       <c r="K17" s="96" t="s">
@@ -47187,7 +47162,7 @@
       <c r="G18" s="97"/>
       <c r="H18" s="338"/>
       <c r="I18" s="21" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="J18" s="93"/>
       <c r="K18" s="96" t="s">
@@ -47215,7 +47190,7 @@
       <c r="G19" s="97"/>
       <c r="H19" s="338"/>
       <c r="I19" s="21" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J19" s="93"/>
       <c r="K19" s="96" t="s">
@@ -47240,7 +47215,7 @@
       <c r="G20" s="97"/>
       <c r="H20" s="338"/>
       <c r="I20" s="21" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="J20" s="93"/>
       <c r="K20" s="91" t="s">
@@ -47265,7 +47240,7 @@
       <c r="G21" s="97"/>
       <c r="H21" s="338"/>
       <c r="I21" s="21" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="J21" s="93"/>
       <c r="K21" s="96" t="s">
@@ -47290,7 +47265,7 @@
       <c r="G22" s="97"/>
       <c r="H22" s="338"/>
       <c r="I22" s="21" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="J22" s="93"/>
       <c r="K22" s="96" t="s">
@@ -47315,7 +47290,7 @@
       <c r="G23" s="97"/>
       <c r="H23" s="338"/>
       <c r="I23" s="21" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="J23" s="93"/>
       <c r="K23" s="96" t="s">
@@ -47340,7 +47315,7 @@
       <c r="G24" s="97"/>
       <c r="H24" s="338"/>
       <c r="I24" s="21" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="J24" s="93"/>
       <c r="K24" s="96" t="s">
@@ -47366,7 +47341,7 @@
       <c r="G25" s="97"/>
       <c r="H25" s="338"/>
       <c r="I25" s="21" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J25" s="93"/>
       <c r="K25" s="96" t="s">
@@ -47414,7 +47389,7 @@
       <c r="G27" s="97"/>
       <c r="H27" s="338"/>
       <c r="I27" s="21" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="J27" s="93"/>
       <c r="K27" s="96" t="s">
@@ -47439,7 +47414,7 @@
       <c r="G28" s="97"/>
       <c r="H28" s="338"/>
       <c r="I28" s="21" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="J28" s="93"/>
       <c r="K28" s="96" t="s">
@@ -47464,7 +47439,7 @@
       <c r="G29" s="97"/>
       <c r="H29" s="338"/>
       <c r="I29" s="21" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J29" s="93"/>
       <c r="K29" s="96" t="s">
@@ -47530,7 +47505,7 @@
         <v>293</v>
       </c>
       <c r="F34" s="381" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G34" s="355"/>
       <c r="H34" s="341"/>
@@ -47702,10 +47677,10 @@
         <v>428</v>
       </c>
       <c r="G43" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I43" s="21"/>
       <c r="J43" s="93"/>
@@ -47718,7 +47693,7 @@
         <v>2</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C44" s="91" t="s">
         <v>95</v>
@@ -47731,7 +47706,7 @@
         <v>99</v>
       </c>
       <c r="G44" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H44" s="95"/>
       <c r="I44" s="21"/>
@@ -47783,7 +47758,7 @@
         <v>99</v>
       </c>
       <c r="G46" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H46" s="93"/>
       <c r="I46" s="21"/>
@@ -47797,7 +47772,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C47" s="91" t="s">
         <v>109</v>
@@ -48013,7 +47988,7 @@
     <row r="56" spans="1:13" ht="51.75" customHeight="1">
       <c r="A56" s="19"/>
       <c r="B56" s="400" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C56" s="389"/>
       <c r="D56" s="389"/>
@@ -48040,7 +48015,7 @@
         <v>293</v>
       </c>
       <c r="F59" s="381" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G59" s="355"/>
       <c r="H59" s="341"/>
@@ -48089,7 +48064,7 @@
         <v>92</v>
       </c>
       <c r="B62" s="359" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C62" s="365"/>
       <c r="D62" s="365"/>
@@ -48206,7 +48181,7 @@
         <v>94</v>
       </c>
       <c r="F68" s="92" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="G68" s="91" t="s">
         <v>95</v>
@@ -48475,7 +48450,7 @@
       <c r="G80" s="91"/>
       <c r="H80" s="19"/>
       <c r="I80" s="21" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J80" s="93"/>
       <c r="K80" s="89" t="s">
@@ -48496,7 +48471,7 @@
       <c r="G81" s="91"/>
       <c r="H81" s="19"/>
       <c r="I81" s="21" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J81" s="93"/>
       <c r="K81" s="89" t="s">
@@ -48535,7 +48510,7 @@
         <v>293</v>
       </c>
       <c r="F84" s="381" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="G84" s="355"/>
       <c r="H84" s="341"/>
@@ -48554,7 +48529,7 @@
         <v>292</v>
       </c>
       <c r="F85" s="364" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G85" s="365"/>
       <c r="H85" s="366"/>
@@ -48584,7 +48559,7 @@
         <v>92</v>
       </c>
       <c r="B87" s="415" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C87" s="365"/>
       <c r="D87" s="365"/>
@@ -48709,7 +48684,7 @@
       </c>
       <c r="H93" s="20"/>
       <c r="I93" s="21" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="J93" s="93"/>
       <c r="K93" s="96" t="s">
@@ -48753,7 +48728,7 @@
     <row r="96" spans="1:13" s="306" customFormat="1">
       <c r="A96" s="19"/>
       <c r="B96" s="385" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C96" s="386"/>
       <c r="D96" s="386"/>
@@ -48761,7 +48736,7 @@
       <c r="F96" s="386"/>
       <c r="G96" s="387"/>
       <c r="H96" s="385" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="I96" s="386"/>
       <c r="J96" s="386"/>
@@ -48782,7 +48757,7 @@
         <v>293</v>
       </c>
       <c r="F98" s="381" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G98" s="355"/>
       <c r="H98" s="341"/>
@@ -48951,10 +48926,10 @@
         <v>204</v>
       </c>
       <c r="G107" s="91" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H107" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I107" s="21"/>
       <c r="J107" s="93"/>
@@ -49272,7 +49247,7 @@
         <v>15</v>
       </c>
       <c r="B121" s="21" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C121" s="93"/>
       <c r="D121" s="89"/>
@@ -49295,7 +49270,7 @@
         <v>16</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C122" s="93"/>
       <c r="D122" s="142"/>
@@ -49498,7 +49473,7 @@
         <v>95</v>
       </c>
       <c r="H134" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I134" s="21"/>
       <c r="J134" s="93"/>
@@ -49788,7 +49763,7 @@
         <v>92</v>
       </c>
       <c r="B154" s="359" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C154" s="365"/>
       <c r="D154" s="365"/>
@@ -50210,7 +50185,7 @@
         <v>14</v>
       </c>
       <c r="B173" s="21" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C173" s="93"/>
       <c r="D173" s="91"/>
@@ -50233,7 +50208,7 @@
         <v>15</v>
       </c>
       <c r="B174" s="21" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C174" s="93"/>
       <c r="D174" s="91"/>
@@ -50261,7 +50236,7 @@
       <c r="G175" s="22"/>
       <c r="H175" s="83"/>
       <c r="I175" s="441" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J175" s="442"/>
       <c r="K175" s="442"/>
@@ -50281,7 +50256,7 @@
         <v>293</v>
       </c>
       <c r="F178" s="381" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G178" s="355"/>
       <c r="H178" s="341"/>
@@ -50330,7 +50305,7 @@
         <v>92</v>
       </c>
       <c r="B181" s="359" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C181" s="365"/>
       <c r="D181" s="365"/>
@@ -50349,7 +50324,7 @@
         <v>285</v>
       </c>
       <c r="B182" s="384" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C182" s="355"/>
       <c r="D182" s="355"/>
@@ -50507,7 +50482,7 @@
       <c r="G190" s="22"/>
       <c r="H190" s="20"/>
       <c r="I190" s="21" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="J190" s="21"/>
       <c r="K190" s="19"/>
@@ -50640,7 +50615,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:M180"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -50998,7 +50973,7 @@
       <c r="F17" s="92"/>
       <c r="G17" s="97"/>
       <c r="H17" s="445" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I17" s="21" t="s">
         <v>124</v>
@@ -51034,7 +51009,7 @@
         <v>99</v>
       </c>
       <c r="M18" s="92" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -51172,7 +51147,7 @@
       <c r="G24" s="97"/>
       <c r="H24" s="446"/>
       <c r="I24" s="21" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J24" s="93"/>
       <c r="K24" s="96" t="s">
@@ -51195,7 +51170,7 @@
       <c r="G25" s="97"/>
       <c r="H25" s="446"/>
       <c r="I25" s="21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J25" s="93"/>
       <c r="K25" s="96" t="s">
@@ -51218,7 +51193,7 @@
       <c r="G26" s="97"/>
       <c r="H26" s="446"/>
       <c r="I26" s="21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J26" s="93"/>
       <c r="K26" s="96" t="s">
@@ -51241,7 +51216,7 @@
       <c r="G27" s="97"/>
       <c r="H27" s="446"/>
       <c r="I27" s="21" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J27" s="93"/>
       <c r="K27" s="96" t="s">
@@ -51251,7 +51226,7 @@
         <v>99</v>
       </c>
       <c r="M27" s="91" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -51266,7 +51241,7 @@
       <c r="G28" s="97"/>
       <c r="H28" s="446"/>
       <c r="I28" s="21" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J28" s="93"/>
       <c r="K28" s="96" t="s">
@@ -51289,11 +51264,11 @@
       <c r="G29" s="97"/>
       <c r="H29" s="447"/>
       <c r="I29" s="21" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J29" s="93"/>
       <c r="K29" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L29" s="92" t="s">
         <v>99</v>
@@ -51667,7 +51642,7 @@
       <c r="G49" s="146"/>
       <c r="H49" s="19"/>
       <c r="I49" s="21" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J49" s="93"/>
       <c r="K49" s="96" t="s">
@@ -51688,7 +51663,7 @@
       <c r="G50" s="146"/>
       <c r="H50" s="19"/>
       <c r="I50" s="21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J50" s="93"/>
       <c r="K50" s="96" t="s">
@@ -51709,7 +51684,7 @@
       <c r="G51" s="146"/>
       <c r="H51" s="19"/>
       <c r="I51" s="21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J51" s="93"/>
       <c r="K51" s="96" t="s">
@@ -51730,7 +51705,7 @@
       <c r="G52" s="146"/>
       <c r="H52" s="19"/>
       <c r="I52" s="21" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J52" s="93"/>
       <c r="K52" s="96" t="s">
@@ -51751,7 +51726,7 @@
       <c r="G53" s="146"/>
       <c r="H53" s="19"/>
       <c r="I53" s="21" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J53" s="93"/>
       <c r="K53" s="96" t="s">
@@ -51772,11 +51747,11 @@
       <c r="G54" s="146"/>
       <c r="H54" s="19"/>
       <c r="I54" s="21" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J54" s="93"/>
       <c r="K54" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L54" s="92" t="s">
         <v>99</v>
@@ -51786,7 +51761,7 @@
     <row r="55" spans="1:13">
       <c r="A55" s="19"/>
       <c r="B55" s="385" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C55" s="386"/>
       <c r="D55" s="386"/>
@@ -52152,7 +52127,7 @@
       <c r="G74" s="146"/>
       <c r="H74" s="19"/>
       <c r="I74" s="21" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J74" s="93"/>
       <c r="K74" s="96" t="s">
@@ -52173,7 +52148,7 @@
       <c r="G75" s="146"/>
       <c r="H75" s="19"/>
       <c r="I75" s="21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J75" s="93"/>
       <c r="K75" s="96" t="s">
@@ -52194,7 +52169,7 @@
       <c r="G76" s="146"/>
       <c r="H76" s="19"/>
       <c r="I76" s="21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J76" s="93"/>
       <c r="K76" s="96" t="s">
@@ -52215,7 +52190,7 @@
       <c r="G77" s="146"/>
       <c r="H77" s="19"/>
       <c r="I77" s="21" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J77" s="93"/>
       <c r="K77" s="96" t="s">
@@ -52236,7 +52211,7 @@
       <c r="G78" s="146"/>
       <c r="H78" s="19"/>
       <c r="I78" s="21" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J78" s="93"/>
       <c r="K78" s="96" t="s">
@@ -52257,11 +52232,11 @@
       <c r="G79" s="146"/>
       <c r="H79" s="19"/>
       <c r="I79" s="21" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J79" s="93"/>
       <c r="K79" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L79" s="92" t="s">
         <v>99</v>
@@ -52271,7 +52246,7 @@
     <row r="80" spans="1:13">
       <c r="A80" s="19"/>
       <c r="B80" s="385" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C80" s="386"/>
       <c r="D80" s="386"/>
@@ -52471,7 +52446,7 @@
         <v>95</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I92" s="21"/>
       <c r="J92" s="93"/>
@@ -52659,7 +52634,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C100" s="93"/>
       <c r="D100" s="96"/>
@@ -52684,7 +52659,7 @@
         <v>10</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C101" s="93"/>
       <c r="D101" s="96"/>
@@ -52709,7 +52684,7 @@
         <v>11</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C102" s="93"/>
       <c r="D102" s="96"/>
@@ -52734,7 +52709,7 @@
         <v>12</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C103" s="93"/>
       <c r="D103" s="96"/>
@@ -52759,7 +52734,7 @@
         <v>13</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C104" s="93"/>
       <c r="D104" s="96"/>
@@ -52784,12 +52759,12 @@
         <v>14</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C105" s="93"/>
       <c r="D105" s="96"/>
       <c r="E105" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F105" s="92" t="s">
         <v>99</v>
@@ -52807,7 +52782,7 @@
     <row r="106" spans="1:13" ht="52.5" customHeight="1">
       <c r="A106" s="19"/>
       <c r="B106" s="400" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C106" s="389"/>
       <c r="D106" s="389"/>
@@ -52883,7 +52858,7 @@
         <v>92</v>
       </c>
       <c r="B112" s="359" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C112" s="365"/>
       <c r="D112" s="365"/>
@@ -53006,7 +52981,7 @@
         <v>95</v>
       </c>
       <c r="H118" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I118" s="21"/>
       <c r="J118" s="93"/>
@@ -53219,7 +53194,7 @@
         <v>10</v>
       </c>
       <c r="B127" s="21" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C127" s="93"/>
       <c r="D127" s="96"/>
@@ -53244,7 +53219,7 @@
         <v>11</v>
       </c>
       <c r="B128" s="21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C128" s="93"/>
       <c r="D128" s="96"/>
@@ -53269,7 +53244,7 @@
         <v>12</v>
       </c>
       <c r="B129" s="21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C129" s="93"/>
       <c r="D129" s="96"/>
@@ -53294,7 +53269,7 @@
         <v>13</v>
       </c>
       <c r="B130" s="21" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C130" s="93"/>
       <c r="D130" s="96"/>
@@ -53319,7 +53294,7 @@
         <v>14</v>
       </c>
       <c r="B131" s="21" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C131" s="93"/>
       <c r="D131" s="96"/>
@@ -53344,12 +53319,12 @@
         <v>15</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C132" s="93"/>
       <c r="D132" s="96"/>
       <c r="E132" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F132" s="92" t="s">
         <v>99</v>
@@ -53564,7 +53539,7 @@
         <v>95</v>
       </c>
       <c r="H145" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I145" s="21"/>
       <c r="J145" s="93"/>
@@ -53777,7 +53752,7 @@
         <v>10</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C154" s="93"/>
       <c r="D154" s="96"/>
@@ -53802,7 +53777,7 @@
         <v>11</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C155" s="93"/>
       <c r="D155" s="96"/>
@@ -53827,7 +53802,7 @@
         <v>12</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C156" s="93"/>
       <c r="D156" s="96"/>
@@ -53852,7 +53827,7 @@
         <v>13</v>
       </c>
       <c r="B157" s="21" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C157" s="93"/>
       <c r="D157" s="96"/>
@@ -53877,7 +53852,7 @@
         <v>14</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C158" s="93"/>
       <c r="D158" s="96"/>
@@ -53902,12 +53877,12 @@
         <v>15</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C159" s="93"/>
       <c r="D159" s="96"/>
       <c r="E159" s="89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F159" s="92" t="s">
         <v>99</v>
@@ -53957,7 +53932,7 @@
         <v>294</v>
       </c>
       <c r="B163" s="380" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C163" s="355"/>
       <c r="D163" s="341"/>
@@ -53965,7 +53940,7 @@
         <v>293</v>
       </c>
       <c r="F163" s="381" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="G163" s="355"/>
       <c r="H163" s="341"/>
@@ -54014,7 +53989,7 @@
         <v>92</v>
       </c>
       <c r="B166" s="359" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C166" s="365"/>
       <c r="D166" s="365"/>
@@ -54138,7 +54113,7 @@
         <v>95</v>
       </c>
       <c r="H172" s="25" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="I172" s="21"/>
       <c r="J172" s="93"/>
@@ -54151,7 +54126,7 @@
         <v>2</v>
       </c>
       <c r="B173" s="246" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C173" s="95"/>
       <c r="D173" s="96"/>
@@ -54176,10 +54151,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="448" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C174" s="93" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D174" s="96"/>
       <c r="E174" s="89" t="s">
@@ -54204,7 +54179,7 @@
       </c>
       <c r="B175" s="419"/>
       <c r="C175" s="93" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D175" s="96"/>
       <c r="E175" s="89" t="s">
@@ -54292,7 +54267,7 @@
     <row r="180" spans="1:13" s="237" customFormat="1" ht="52.5" customHeight="1">
       <c r="A180" s="19"/>
       <c r="B180" s="400" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C180" s="389"/>
       <c r="D180" s="389"/>
@@ -54419,7 +54394,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:M149"/>
   <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -54828,7 +54803,7 @@
       <c r="G19" s="97"/>
       <c r="H19" s="338"/>
       <c r="I19" s="21" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="J19" s="93"/>
       <c r="K19" s="96" t="s">
@@ -54851,7 +54826,7 @@
       <c r="G20" s="97"/>
       <c r="H20" s="338"/>
       <c r="I20" s="21" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="J20" s="93"/>
       <c r="K20" s="96" t="s">
@@ -54876,7 +54851,7 @@
       <c r="G21" s="97"/>
       <c r="H21" s="338"/>
       <c r="I21" s="21" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="J21" s="93"/>
       <c r="K21" s="96" t="s">
@@ -54899,7 +54874,7 @@
       <c r="G22" s="97"/>
       <c r="H22" s="338"/>
       <c r="I22" s="21" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="J22" s="93"/>
       <c r="K22" s="96" t="s">
@@ -54922,7 +54897,7 @@
       <c r="G23" s="97"/>
       <c r="H23" s="338"/>
       <c r="I23" s="21" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="J23" s="93"/>
       <c r="K23" s="96" t="s">
@@ -54945,7 +54920,7 @@
       <c r="G24" s="97"/>
       <c r="H24" s="338"/>
       <c r="I24" s="21" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="J24" s="93"/>
       <c r="K24" s="96" t="s">
@@ -54968,7 +54943,7 @@
       <c r="G25" s="97"/>
       <c r="H25" s="338"/>
       <c r="I25" s="21" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="J25" s="93"/>
       <c r="K25" s="96" t="s">
@@ -54991,7 +54966,7 @@
       <c r="G26" s="97"/>
       <c r="H26" s="338"/>
       <c r="I26" s="21" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="J26" s="93"/>
       <c r="K26" s="96" t="s">
@@ -55104,7 +55079,7 @@
         <v>92</v>
       </c>
       <c r="B34" s="359" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C34" s="365"/>
       <c r="D34" s="365"/>
@@ -55620,7 +55595,7 @@
     <row r="57" spans="1:13">
       <c r="A57" s="19"/>
       <c r="B57" s="385" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C57" s="386"/>
       <c r="D57" s="386"/>
@@ -55818,7 +55793,7 @@
       </c>
       <c r="G69" s="91"/>
       <c r="H69" s="20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I69" s="21"/>
       <c r="J69" s="93"/>
@@ -56122,7 +56097,7 @@
         <v>293</v>
       </c>
       <c r="F85" s="381" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G85" s="355"/>
       <c r="H85" s="341"/>
@@ -56171,7 +56146,7 @@
         <v>92</v>
       </c>
       <c r="B88" s="359" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C88" s="365"/>
       <c r="D88" s="365"/>
@@ -56294,7 +56269,7 @@
         <v>95</v>
       </c>
       <c r="H94" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I94" s="21"/>
       <c r="J94" s="93"/>
@@ -56332,7 +56307,7 @@
         <v>3</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C96" s="93"/>
       <c r="D96" s="96"/>
@@ -56655,7 +56630,7 @@
         <v>293</v>
       </c>
       <c r="F111" s="381" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G111" s="355"/>
       <c r="H111" s="341"/>
@@ -56875,7 +56850,7 @@
         <v>3</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C122" s="93"/>
       <c r="D122" s="96"/>
@@ -57142,7 +57117,7 @@
         <v>293</v>
       </c>
       <c r="F137" s="381" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="G137" s="355"/>
       <c r="H137" s="341"/>
@@ -57191,7 +57166,7 @@
         <v>92</v>
       </c>
       <c r="B140" s="415" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C140" s="365"/>
       <c r="D140" s="365"/>
@@ -57316,7 +57291,7 @@
         <v>95</v>
       </c>
       <c r="H146" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I146" s="21"/>
       <c r="J146" s="93"/>
@@ -57354,7 +57329,7 @@
         <v>3</v>
       </c>
       <c r="B148" s="21" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C148" s="93"/>
       <c r="D148" s="96"/>
@@ -57375,7 +57350,7 @@
     <row r="149" spans="1:13" ht="48.75" customHeight="1">
       <c r="A149" s="120"/>
       <c r="B149" s="449" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C149" s="450"/>
       <c r="D149" s="450"/>
